--- a/data/bist_screener_2026-05-12.xlsx
+++ b/data/bist_screener_2026-05-12.xlsx
@@ -642,42 +642,42 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AZTEK</t>
+          <t>SNGYO</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4.98</v>
+        <v>3.81</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0.0353</v>
+        <v>-0.0256</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>22480000</v>
+        <v>44050000</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>0.25</v>
+        <v>0.4221</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>63.74</v>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
+        <v>52.66</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>18.48</v>
+      </c>
       <c r="H4" s="3" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>-0.2178</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>-2.871</v>
-      </c>
+        <v>0.0163</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr"/>
@@ -685,42 +685,42 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>ZOREN</t>
+          <t>AZTEK</t>
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>3.38</v>
+        <v>4.98</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>-0.0117</v>
+        <v>0.0353</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>85480000</v>
+        <v>22480000</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>0.3779999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>68.09</v>
+        <v>63.74</v>
       </c>
       <c r="G5" s="6" t="inlineStr"/>
       <c r="H5" s="7" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="I5" s="8" t="n">
-        <v>-0.22</v>
+        <v>-0.2178</v>
       </c>
       <c r="J5" s="8" t="n">
-        <v>0.6995999999999999</v>
+        <v>-2.871</v>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST ELEKTRIK, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HİZMETLER, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST BURSA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr"/>
@@ -728,42 +728,42 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>OZKGY</t>
+          <t>ZOREN</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>12.84</v>
+        <v>3.38</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.0418</v>
+        <v>-0.0117</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>9450000</v>
+        <v>85480000</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.2681</v>
+        <v>0.3779999999999999</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>48.58</v>
+        <v>68.09</v>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="3" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.0037</v>
+        <v>-0.22</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-2.3084</v>
+        <v>0.6995999999999999</v>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST YILDIZ</t>
+          <t>BIST 100, BIST ELEKTRIK, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HİZMETLER, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST BURSA</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr"/>
@@ -771,35 +771,33 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>SNGYO</t>
+          <t>OZKGY</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>3.81</v>
+        <v>12.84</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>-0.0256</v>
+        <v>-0.0418</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>44050000</v>
+        <v>9450000</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>0.4221</v>
+        <v>0.2681</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>52.66</v>
-      </c>
-      <c r="G7" s="7" t="n">
-        <v>28.95</v>
-      </c>
+        <v>48.58</v>
+      </c>
+      <c r="G7" s="6" t="inlineStr"/>
       <c r="H7" s="7" t="n">
         <v>0.29</v>
       </c>
       <c r="I7" s="8" t="n">
-        <v>0.0115</v>
+        <v>-0.0037</v>
       </c>
       <c r="J7" s="8" t="n">
-        <v>-13.0614</v>
+        <v>-2.3084</v>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
@@ -808,7 +806,7 @@
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M7" s="6" t="inlineStr"/>
@@ -6354,42 +6352,40 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>BLCYT</t>
+          <t>ALGYO</t>
         </is>
       </c>
       <c r="B136" s="3" t="n">
-        <v>35.26</v>
+        <v>7.21</v>
       </c>
       <c r="C136" s="4" t="n">
-        <v>-0.0527</v>
+        <v>0.0464</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>3630000</v>
+        <v>156180000</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>0.3318</v>
+        <v>0.4379</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>45.65</v>
-      </c>
-      <c r="G136" s="3" t="n">
-        <v>93.26000000000001</v>
-      </c>
+        <v>69.84</v>
+      </c>
+      <c r="G136" s="2" t="inlineStr"/>
       <c r="H136" s="3" t="n">
         <v>0.83</v>
       </c>
       <c r="I136" s="4" t="n">
-        <v>0.0159</v>
+        <v>-0.1298</v>
       </c>
       <c r="J136" s="2" t="inlineStr"/>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST ANA, ADANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M136" s="2" t="inlineStr"/>
@@ -6397,126 +6393,124 @@
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>BRKO</t>
+          <t>BLCYT</t>
         </is>
       </c>
       <c r="B137" s="7" t="n">
-        <v>12.66</v>
+        <v>35.26</v>
       </c>
       <c r="C137" s="8" t="n">
-        <v>-0.0262</v>
+        <v>-0.0527</v>
       </c>
       <c r="D137" s="9" t="n">
-        <v>497940</v>
-      </c>
-      <c r="E137" s="6" t="inlineStr"/>
+        <v>3630000</v>
+      </c>
+      <c r="E137" s="8" t="n">
+        <v>0.3318</v>
+      </c>
       <c r="F137" s="7" t="n">
-        <v>40.54</v>
+        <v>45.65</v>
       </c>
       <c r="G137" s="7" t="n">
-        <v>12.68</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="H137" s="7" t="n">
         <v>0.83</v>
       </c>
       <c r="I137" s="8" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.0159</v>
       </c>
       <c r="J137" s="6" t="inlineStr"/>
       <c r="K137" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
-        </is>
-      </c>
-      <c r="L137" s="6" t="inlineStr"/>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L137" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST ANA, ADANA</t>
+        </is>
+      </c>
       <c r="M137" s="6" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>A1CAP</t>
+          <t>BRKO</t>
         </is>
       </c>
       <c r="B138" s="3" t="n">
-        <v>11.43</v>
+        <v>12.66</v>
       </c>
       <c r="C138" s="4" t="n">
-        <v>-0.0289</v>
+        <v>-0.0262</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>21400000</v>
-      </c>
-      <c r="E138" s="4" t="n">
-        <v>0.7115</v>
-      </c>
+        <v>497940</v>
+      </c>
+      <c r="E138" s="2" t="inlineStr"/>
       <c r="F138" s="3" t="n">
-        <v>29.07</v>
+        <v>40.54</v>
       </c>
       <c r="G138" s="3" t="n">
-        <v>2.07</v>
+        <v>12.68</v>
       </c>
       <c r="H138" s="3" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="I138" s="4" t="n">
-        <v>0.5625</v>
-      </c>
-      <c r="J138" s="4" t="n">
-        <v>4.1559</v>
-      </c>
+        <v>0.07679999999999999</v>
+      </c>
+      <c r="J138" s="2" t="inlineStr"/>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L138" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST MALİ, BIST ARACI KURUMLAR, BIST YILDIZ</t>
-        </is>
-      </c>
+          <t>Dayanıklı tüketim malları</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="inlineStr"/>
       <c r="M138" s="2" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>GOKNR</t>
+          <t>A1CAP</t>
         </is>
       </c>
       <c r="B139" s="7" t="n">
-        <v>23.5</v>
+        <v>11.43</v>
       </c>
       <c r="C139" s="8" t="n">
-        <v>0.0147</v>
+        <v>-0.0289</v>
       </c>
       <c r="D139" s="9" t="n">
-        <v>7510000</v>
+        <v>21400000</v>
       </c>
       <c r="E139" s="8" t="n">
-        <v>0.2656</v>
+        <v>0.7115</v>
       </c>
       <c r="F139" s="7" t="n">
-        <v>65.33</v>
+        <v>29.07</v>
       </c>
       <c r="G139" s="7" t="n">
-        <v>19.9</v>
+        <v>2.07</v>
       </c>
       <c r="H139" s="7" t="n">
         <v>0.84</v>
       </c>
       <c r="I139" s="8" t="n">
-        <v>0.0488</v>
+        <v>0.5625</v>
       </c>
       <c r="J139" s="8" t="n">
-        <v>-3.3307</v>
+        <v>4.1559</v>
       </c>
       <c r="K139" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L139" s="6" t="inlineStr">
         <is>
-          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST MALİ, BIST ARACI KURUMLAR, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M139" s="6" t="inlineStr"/>
@@ -6524,44 +6518,44 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>ISCTR</t>
+          <t>GOKNR</t>
         </is>
       </c>
       <c r="B140" s="3" t="n">
-        <v>14.27</v>
+        <v>23.5</v>
       </c>
       <c r="C140" s="4" t="n">
-        <v>-0.0325</v>
-      </c>
-      <c r="D140" s="3" t="n">
-        <v>527590000.0000001</v>
+        <v>0.0147</v>
+      </c>
+      <c r="D140" s="5" t="n">
+        <v>7510000</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>0.3325</v>
+        <v>0.2656</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>48.45</v>
+        <v>65.33</v>
       </c>
       <c r="G140" s="3" t="n">
-        <v>4.68</v>
+        <v>19.9</v>
       </c>
       <c r="H140" s="3" t="n">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="I140" s="4" t="n">
-        <v>0.2039</v>
+        <v>0.0488</v>
       </c>
       <c r="J140" s="4" t="n">
-        <v>-0.1384</v>
+        <v>-3.3307</v>
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 30, BIST BANKA, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST LİKİT BANKA, BIST MALİ, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500, STOXX Eastern Europe 50</t>
+          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M140" s="2" t="inlineStr"/>
@@ -6569,44 +6563,44 @@
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>YYLGD</t>
+          <t>ISCTR</t>
         </is>
       </c>
       <c r="B141" s="7" t="n">
-        <v>12.53</v>
+        <v>14.27</v>
       </c>
       <c r="C141" s="8" t="n">
-        <v>0.0089</v>
-      </c>
-      <c r="D141" s="9" t="n">
-        <v>11510000</v>
+        <v>-0.0325</v>
+      </c>
+      <c r="D141" s="7" t="n">
+        <v>527590000.0000001</v>
       </c>
       <c r="E141" s="8" t="n">
-        <v>0.9348000000000001</v>
+        <v>0.3325</v>
       </c>
       <c r="F141" s="7" t="n">
-        <v>62.64</v>
+        <v>48.45</v>
       </c>
       <c r="G141" s="7" t="n">
-        <v>17.06</v>
+        <v>4.68</v>
       </c>
       <c r="H141" s="7" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="I141" s="8" t="n">
-        <v>0.0588</v>
+        <v>0.2039</v>
       </c>
       <c r="J141" s="8" t="n">
-        <v>11.314</v>
+        <v>-0.1384</v>
       </c>
       <c r="K141" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L141" s="6" t="inlineStr">
         <is>
-          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST YILDIZ, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST 100, BIST 30, BIST BANKA, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST LİKİT BANKA, BIST MALİ, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500, STOXX Eastern Europe 50</t>
         </is>
       </c>
       <c r="M141" s="6" t="inlineStr"/>
@@ -6614,44 +6608,44 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>ZEDUR</t>
+          <t>YYLGD</t>
         </is>
       </c>
       <c r="B142" s="3" t="n">
-        <v>11.22</v>
+        <v>12.53</v>
       </c>
       <c r="C142" s="4" t="n">
-        <v>0.0145</v>
+        <v>0.0089</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>11930000</v>
+        <v>11510000</v>
       </c>
       <c r="E142" s="4" t="n">
-        <v>0.467</v>
+        <v>0.9348000000000001</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>84.12</v>
+        <v>62.64</v>
       </c>
       <c r="G142" s="3" t="n">
-        <v>124.67</v>
+        <v>17.06</v>
       </c>
       <c r="H142" s="3" t="n">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="I142" s="4" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.0588</v>
       </c>
       <c r="J142" s="4" t="n">
-        <v>-113.1382</v>
+        <v>11.314</v>
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>Tüketici hizmetleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST KATILIM TÜM, BIST ANA, BIST ANKARA</t>
+          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST YILDIZ, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M142" s="2" t="inlineStr"/>
@@ -6659,42 +6653,44 @@
     <row r="143">
       <c r="A143" s="6" t="inlineStr">
         <is>
-          <t>CEMTS</t>
+          <t>ZEDUR</t>
         </is>
       </c>
       <c r="B143" s="7" t="n">
-        <v>11.39</v>
+        <v>11.22</v>
       </c>
       <c r="C143" s="8" t="n">
-        <v>-0.0437</v>
+        <v>0.0145</v>
       </c>
       <c r="D143" s="9" t="n">
-        <v>4090000</v>
+        <v>11930000</v>
       </c>
       <c r="E143" s="8" t="n">
-        <v>0.3352000000000001</v>
+        <v>0.467</v>
       </c>
       <c r="F143" s="7" t="n">
-        <v>55.52</v>
-      </c>
-      <c r="G143" s="6" t="inlineStr"/>
+        <v>84.12</v>
+      </c>
+      <c r="G143" s="7" t="n">
+        <v>124.67</v>
+      </c>
       <c r="H143" s="7" t="n">
         <v>0.87</v>
       </c>
       <c r="I143" s="8" t="n">
-        <v>-0.0184</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="J143" s="8" t="n">
-        <v>-18.3247</v>
+        <v>-113.1382</v>
       </c>
       <c r="K143" s="6" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Tüketici hizmetleri</t>
         </is>
       </c>
       <c r="L143" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST BURSA</t>
+          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST KATILIM TÜM, BIST ANA, BIST ANKARA</t>
         </is>
       </c>
       <c r="M143" s="6" t="inlineStr"/>
@@ -6702,42 +6698,42 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>PAHOL</t>
+          <t>CEMTS</t>
         </is>
       </c>
       <c r="B144" s="3" t="n">
-        <v>1.74</v>
+        <v>11.39</v>
       </c>
       <c r="C144" s="4" t="n">
-        <v>-0.0279</v>
+        <v>-0.0437</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>622460000</v>
+        <v>4090000</v>
       </c>
       <c r="E144" s="4" t="n">
-        <v>0.2</v>
+        <v>0.3352000000000001</v>
       </c>
       <c r="F144" s="3" t="n">
-        <v>63.66</v>
+        <v>55.52</v>
       </c>
       <c r="G144" s="2" t="inlineStr"/>
       <c r="H144" s="3" t="n">
         <v>0.87</v>
       </c>
       <c r="I144" s="4" t="n">
-        <v>0.1267</v>
+        <v>-0.0184</v>
       </c>
       <c r="J144" s="4" t="n">
-        <v>-0.3898</v>
+        <v>-18.3247</v>
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>Çeşitli Hizmetler</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST HALKA ARZ, BIST MALİ, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST ANKARA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST BURSA</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr"/>
@@ -6745,44 +6741,42 @@
     <row r="145">
       <c r="A145" s="6" t="inlineStr">
         <is>
-          <t>AYGAZ</t>
+          <t>PAHOL</t>
         </is>
       </c>
       <c r="B145" s="7" t="n">
-        <v>286.25</v>
+        <v>1.74</v>
       </c>
       <c r="C145" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D145" s="7" t="n">
-        <v>514049.9999999999</v>
+        <v>-0.0279</v>
+      </c>
+      <c r="D145" s="9" t="n">
+        <v>622460000</v>
       </c>
       <c r="E145" s="8" t="n">
-        <v>0.2427</v>
+        <v>0.2</v>
       </c>
       <c r="F145" s="7" t="n">
-        <v>58.69</v>
-      </c>
-      <c r="G145" s="7" t="n">
-        <v>12.47</v>
-      </c>
+        <v>63.66</v>
+      </c>
+      <c r="G145" s="6" t="inlineStr"/>
       <c r="H145" s="7" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="I145" s="8" t="n">
-        <v>0.08070000000000001</v>
+        <v>0.1267</v>
       </c>
       <c r="J145" s="8" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.3898</v>
       </c>
       <c r="K145" s="6" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Çeşitli Hizmetler</t>
         </is>
       </c>
       <c r="L145" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST İSTANBUL, BIST YILDIZ, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST HALKA ARZ, BIST MALİ, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST ANKARA</t>
         </is>
       </c>
       <c r="M145" s="6" t="inlineStr"/>
@@ -6790,42 +6784,44 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>ECILC</t>
+          <t>AYGAZ</t>
         </is>
       </c>
       <c r="B146" s="3" t="n">
-        <v>85.75</v>
+        <v>286.25</v>
       </c>
       <c r="C146" s="4" t="n">
-        <v>-0.0338</v>
-      </c>
-      <c r="D146" s="5" t="n">
-        <v>9020000</v>
+        <v>0</v>
+      </c>
+      <c r="D146" s="3" t="n">
+        <v>514049.9999999999</v>
       </c>
       <c r="E146" s="4" t="n">
-        <v>0.1877</v>
+        <v>0.2427</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>36.78</v>
-      </c>
-      <c r="G146" s="2" t="inlineStr"/>
+        <v>58.69</v>
+      </c>
+      <c r="G146" s="3" t="n">
+        <v>12.47</v>
+      </c>
       <c r="H146" s="3" t="n">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="I146" s="4" t="n">
-        <v>-0.0104</v>
+        <v>0.08070000000000001</v>
       </c>
       <c r="J146" s="4" t="n">
-        <v>-0.9183</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>Sağlık teknolojisi</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST İSTANBUL, BIST YILDIZ, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M146" s="2" t="inlineStr"/>
@@ -6833,42 +6829,42 @@
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
         <is>
-          <t>ALGYO</t>
+          <t>ECILC</t>
         </is>
       </c>
       <c r="B147" s="7" t="n">
-        <v>7.21</v>
+        <v>85.75</v>
       </c>
       <c r="C147" s="8" t="n">
-        <v>0.0464</v>
+        <v>-0.0338</v>
       </c>
       <c r="D147" s="9" t="n">
-        <v>156180000</v>
+        <v>9020000</v>
       </c>
       <c r="E147" s="8" t="n">
-        <v>0.4379</v>
+        <v>0.1877</v>
       </c>
       <c r="F147" s="7" t="n">
-        <v>69.84</v>
+        <v>36.78</v>
       </c>
       <c r="G147" s="6" t="inlineStr"/>
       <c r="H147" s="7" t="n">
         <v>0.89</v>
       </c>
       <c r="I147" s="8" t="n">
-        <v>-0.1411</v>
+        <v>-0.0104</v>
       </c>
       <c r="J147" s="8" t="n">
-        <v>-8.579000000000001</v>
+        <v>-0.9183</v>
       </c>
       <c r="K147" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Sağlık teknolojisi</t>
         </is>
       </c>
       <c r="L147" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST YILDIZ</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU</t>
         </is>
       </c>
       <c r="M147" s="6" t="inlineStr"/>
@@ -9955,35 +9951,35 @@
     <row r="219">
       <c r="A219" s="6" t="inlineStr">
         <is>
-          <t>GARAN</t>
+          <t>OYYAT</t>
         </is>
       </c>
       <c r="B219" s="7" t="n">
-        <v>133.4</v>
+        <v>53.35</v>
       </c>
       <c r="C219" s="8" t="n">
-        <v>-0.0347</v>
+        <v>-0.022</v>
       </c>
       <c r="D219" s="9" t="n">
-        <v>34620000</v>
+        <v>645070</v>
       </c>
       <c r="E219" s="8" t="n">
-        <v>0.1403</v>
+        <v>0.3035</v>
       </c>
       <c r="F219" s="7" t="n">
-        <v>45.74</v>
+        <v>41.66</v>
       </c>
       <c r="G219" s="7" t="n">
-        <v>4.75</v>
+        <v>7.74</v>
       </c>
       <c r="H219" s="7" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="I219" s="8" t="n">
-        <v>0.2974</v>
+        <v>0.1958</v>
       </c>
       <c r="J219" s="8" t="n">
-        <v>0.2559</v>
+        <v>-1.1768</v>
       </c>
       <c r="K219" s="6" t="inlineStr">
         <is>
@@ -9992,7 +9988,7 @@
       </c>
       <c r="L219" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 30, BIST BANKA, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST LİKİT BANKA, BIST MALİ, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500</t>
+          <t>BIST TUM-100, BIST TÜM, BIST MALİ, BIST ARACI KURUMLAR, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M219" s="6" t="inlineStr"/>
@@ -10000,44 +9996,44 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>TATGD</t>
+          <t>GARAN</t>
         </is>
       </c>
       <c r="B220" s="3" t="n">
-        <v>21.86</v>
+        <v>133.4</v>
       </c>
       <c r="C220" s="4" t="n">
-        <v>0.09960000000000001</v>
+        <v>-0.0347</v>
       </c>
       <c r="D220" s="5" t="n">
-        <v>11640000</v>
+        <v>34620000</v>
       </c>
       <c r="E220" s="4" t="n">
-        <v>0.4189</v>
+        <v>0.1403</v>
       </c>
       <c r="F220" s="3" t="n">
-        <v>69.81999999999999</v>
+        <v>45.74</v>
       </c>
       <c r="G220" s="3" t="n">
-        <v>37.19</v>
+        <v>4.75</v>
       </c>
       <c r="H220" s="3" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="I220" s="4" t="n">
-        <v>0.039</v>
+        <v>0.2974</v>
       </c>
       <c r="J220" s="4" t="n">
-        <v>2.881</v>
+        <v>0.2559</v>
       </c>
       <c r="K220" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L220" s="2" t="inlineStr">
         <is>
-          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST ANA, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST BURSA</t>
+          <t>BIST 100, BIST 30, BIST BANKA, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST LİKİT BANKA, BIST MALİ, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500</t>
         </is>
       </c>
       <c r="M220" s="2" t="inlineStr"/>
@@ -10045,44 +10041,44 @@
     <row r="221">
       <c r="A221" s="6" t="inlineStr">
         <is>
-          <t>AKBNK</t>
+          <t>TATGD</t>
         </is>
       </c>
       <c r="B221" s="7" t="n">
-        <v>72.75</v>
+        <v>21.86</v>
       </c>
       <c r="C221" s="8" t="n">
-        <v>-0.0409</v>
+        <v>0.09960000000000001</v>
       </c>
       <c r="D221" s="9" t="n">
-        <v>139150000</v>
+        <v>11640000</v>
       </c>
       <c r="E221" s="8" t="n">
-        <v>0.5871999999999999</v>
+        <v>0.4189</v>
       </c>
       <c r="F221" s="7" t="n">
-        <v>44.05</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="G221" s="7" t="n">
-        <v>6.04</v>
+        <v>37.19</v>
       </c>
       <c r="H221" s="7" t="n">
         <v>1.25</v>
       </c>
       <c r="I221" s="8" t="n">
-        <v>0.2298</v>
+        <v>0.039</v>
       </c>
       <c r="J221" s="8" t="n">
-        <v>0.0447</v>
+        <v>2.881</v>
       </c>
       <c r="K221" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L221" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 30, BIST BANKA, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST LİKİT BANKA, BIST MALİ, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500, STOXX Eastern Europe 50</t>
+          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST ANA, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST BURSA</t>
         </is>
       </c>
       <c r="M221" s="6" t="inlineStr"/>
@@ -10090,44 +10086,44 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>INDES</t>
+          <t>AKBNK</t>
         </is>
       </c>
       <c r="B222" s="3" t="n">
-        <v>11.22</v>
+        <v>72.75</v>
       </c>
       <c r="C222" s="4" t="n">
-        <v>-0.05</v>
+        <v>-0.0409</v>
       </c>
       <c r="D222" s="5" t="n">
-        <v>12610000</v>
+        <v>139150000</v>
       </c>
       <c r="E222" s="4" t="n">
-        <v>0.599</v>
+        <v>0.5871999999999999</v>
       </c>
       <c r="F222" s="3" t="n">
-        <v>66.75</v>
+        <v>44.05</v>
       </c>
       <c r="G222" s="3" t="n">
-        <v>16.9</v>
+        <v>6.04</v>
       </c>
       <c r="H222" s="3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="I222" s="4" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.2298</v>
       </c>
       <c r="J222" s="4" t="n">
-        <v>0.6942</v>
+        <v>0.0447</v>
       </c>
       <c r="K222" s="2" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L222" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST YILDIZ, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
+          <t>BIST 100, BIST 30, BIST BANKA, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST LİKİT BANKA, BIST MALİ, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500, STOXX Eastern Europe 50</t>
         </is>
       </c>
       <c r="M222" s="2" t="inlineStr"/>
@@ -10135,44 +10131,44 @@
     <row r="223">
       <c r="A223" s="6" t="inlineStr">
         <is>
-          <t>BASGZ</t>
+          <t>INDES</t>
         </is>
       </c>
       <c r="B223" s="7" t="n">
-        <v>51.55</v>
+        <v>11.22</v>
       </c>
       <c r="C223" s="8" t="n">
-        <v>0.0039</v>
+        <v>-0.05</v>
       </c>
       <c r="D223" s="9" t="n">
-        <v>700610</v>
+        <v>12610000</v>
       </c>
       <c r="E223" s="8" t="n">
-        <v>0.25</v>
+        <v>0.599</v>
       </c>
       <c r="F223" s="7" t="n">
-        <v>57.65</v>
+        <v>66.75</v>
       </c>
       <c r="G223" s="7" t="n">
-        <v>11.67</v>
+        <v>16.9</v>
       </c>
       <c r="H223" s="7" t="n">
         <v>1.26</v>
       </c>
       <c r="I223" s="8" t="n">
-        <v>0.1261</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="J223" s="8" t="n">
-        <v>1.3131</v>
+        <v>0.6942</v>
       </c>
       <c r="K223" s="6" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="L223" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST KATILIM TEMETTU</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST YILDIZ, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI</t>
         </is>
       </c>
       <c r="M223" s="6" t="inlineStr"/>
@@ -10180,44 +10176,44 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>KRSTL</t>
+          <t>BASGZ</t>
         </is>
       </c>
       <c r="B224" s="3" t="n">
-        <v>11.46</v>
+        <v>51.55</v>
       </c>
       <c r="C224" s="4" t="n">
-        <v>0.0495</v>
+        <v>0.0039</v>
       </c>
       <c r="D224" s="5" t="n">
-        <v>23960000</v>
+        <v>700610</v>
       </c>
       <c r="E224" s="4" t="n">
-        <v>0.9556</v>
+        <v>0.25</v>
       </c>
       <c r="F224" s="3" t="n">
-        <v>75.05</v>
+        <v>57.65</v>
       </c>
       <c r="G224" s="3" t="n">
-        <v>7.79</v>
+        <v>11.67</v>
       </c>
       <c r="H224" s="3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="I224" s="4" t="n">
-        <v>0.2011</v>
+        <v>0.1261</v>
       </c>
       <c r="J224" s="4" t="n">
-        <v>0.6818000000000001</v>
+        <v>1.3131</v>
       </c>
       <c r="K224" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="L224" s="2" t="inlineStr">
         <is>
-          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM TÜM, BIST ANA, BIST BALIKESİR</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST KATILIM TEMETTU</t>
         </is>
       </c>
       <c r="M224" s="2" t="inlineStr"/>
@@ -10225,44 +10221,44 @@
     <row r="225">
       <c r="A225" s="6" t="inlineStr">
         <is>
-          <t>TAVHL</t>
+          <t>KRSTL</t>
         </is>
       </c>
       <c r="B225" s="7" t="n">
-        <v>269.25</v>
+        <v>11.46</v>
       </c>
       <c r="C225" s="8" t="n">
-        <v>-0.0349</v>
+        <v>0.0495</v>
       </c>
       <c r="D225" s="9" t="n">
-        <v>4010000</v>
+        <v>23960000</v>
       </c>
       <c r="E225" s="8" t="n">
-        <v>0.4979</v>
+        <v>0.9556</v>
       </c>
       <c r="F225" s="7" t="n">
-        <v>34.66</v>
+        <v>75.05</v>
       </c>
       <c r="G225" s="7" t="n">
-        <v>62.54</v>
+        <v>7.79</v>
       </c>
       <c r="H225" s="7" t="n">
         <v>1.27</v>
       </c>
       <c r="I225" s="8" t="n">
-        <v>0.0226</v>
+        <v>0.2011</v>
       </c>
       <c r="J225" s="8" t="n">
-        <v>-1.474</v>
+        <v>0.6818000000000001</v>
       </c>
       <c r="K225" s="6" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L225" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST 50, BIST MALİ, BIST İSTANBUL, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500</t>
+          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST KATILIM TÜM, BIST ANA, BIST BALIKESİR</t>
         </is>
       </c>
       <c r="M225" s="6" t="inlineStr"/>
@@ -10270,38 +10266,44 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>DOFER</t>
+          <t>TAVHL</t>
         </is>
       </c>
       <c r="B226" s="3" t="n">
-        <v>35.36</v>
+        <v>269.25</v>
       </c>
       <c r="C226" s="4" t="n">
-        <v>0.004</v>
+        <v>-0.0349</v>
       </c>
       <c r="D226" s="5" t="n">
-        <v>1780000</v>
-      </c>
-      <c r="E226" s="2" t="inlineStr"/>
+        <v>4010000</v>
+      </c>
+      <c r="E226" s="4" t="n">
+        <v>0.4979</v>
+      </c>
       <c r="F226" s="3" t="n">
-        <v>56.75</v>
-      </c>
-      <c r="G226" s="2" t="inlineStr"/>
+        <v>34.66</v>
+      </c>
+      <c r="G226" s="3" t="n">
+        <v>62.54</v>
+      </c>
       <c r="H226" s="3" t="n">
         <v>1.27</v>
       </c>
-      <c r="I226" s="2" t="inlineStr"/>
+      <c r="I226" s="4" t="n">
+        <v>0.0226</v>
+      </c>
       <c r="J226" s="4" t="n">
-        <v>-2.7319</v>
+        <v>-1.474</v>
       </c>
       <c r="K226" s="2" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Taşımacılık</t>
         </is>
       </c>
       <c r="L226" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST 50, BIST MALİ, BIST İSTANBUL, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500</t>
         </is>
       </c>
       <c r="M226" s="2" t="inlineStr"/>
@@ -10309,44 +10311,38 @@
     <row r="227">
       <c r="A227" s="6" t="inlineStr">
         <is>
-          <t>ZRGYO</t>
+          <t>DOFER</t>
         </is>
       </c>
       <c r="B227" s="7" t="n">
-        <v>21.5</v>
+        <v>35.36</v>
       </c>
       <c r="C227" s="8" t="n">
-        <v>-0.0218</v>
+        <v>0.004</v>
       </c>
       <c r="D227" s="9" t="n">
-        <v>973920</v>
-      </c>
-      <c r="E227" s="8" t="n">
-        <v>1</v>
-      </c>
+        <v>1780000</v>
+      </c>
+      <c r="E227" s="6" t="inlineStr"/>
       <c r="F227" s="7" t="n">
-        <v>46.26</v>
-      </c>
-      <c r="G227" s="7" t="n">
-        <v>13.66</v>
-      </c>
+        <v>56.75</v>
+      </c>
+      <c r="G227" s="6" t="inlineStr"/>
       <c r="H227" s="7" t="n">
         <v>1.27</v>
       </c>
-      <c r="I227" s="8" t="n">
-        <v>0.11</v>
-      </c>
+      <c r="I227" s="6" t="inlineStr"/>
       <c r="J227" s="8" t="n">
-        <v>11.4715</v>
+        <v>-2.7319</v>
       </c>
       <c r="K227" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="L227" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST YILDIZ, BIST TEMETTU</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M227" s="6" t="inlineStr"/>
@@ -10354,44 +10350,44 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>MEDTR</t>
+          <t>ZRGYO</t>
         </is>
       </c>
       <c r="B228" s="3" t="n">
-        <v>31.18</v>
+        <v>21.5</v>
       </c>
       <c r="C228" s="4" t="n">
-        <v>-0.04650000000000001</v>
+        <v>-0.0218</v>
       </c>
       <c r="D228" s="5" t="n">
-        <v>1500000</v>
+        <v>973920</v>
       </c>
       <c r="E228" s="4" t="n">
-        <v>0.2059</v>
+        <v>1</v>
       </c>
       <c r="F228" s="3" t="n">
-        <v>57.52</v>
+        <v>46.26</v>
       </c>
       <c r="G228" s="3" t="n">
-        <v>1889.7</v>
+        <v>13.66</v>
       </c>
       <c r="H228" s="3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="I228" s="4" t="n">
-        <v>0.0008</v>
+        <v>0.11</v>
       </c>
       <c r="J228" s="4" t="n">
-        <v>1.5318</v>
+        <v>11.4715</v>
       </c>
       <c r="K228" s="2" t="inlineStr">
         <is>
-          <t>Sağlık teknolojisi</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L228" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM, BIST ANA, BIST İZMİR</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST MALİ, BIST YILDIZ, BIST TEMETTU</t>
         </is>
       </c>
       <c r="M228" s="2" t="inlineStr"/>
@@ -10399,44 +10395,44 @@
     <row r="229">
       <c r="A229" s="6" t="inlineStr">
         <is>
-          <t>KLSYN</t>
+          <t>MEDTR</t>
         </is>
       </c>
       <c r="B229" s="7" t="n">
-        <v>11.31</v>
+        <v>31.18</v>
       </c>
       <c r="C229" s="8" t="n">
-        <v>-0.0275</v>
+        <v>-0.04650000000000001</v>
       </c>
       <c r="D229" s="9" t="n">
-        <v>11290000</v>
+        <v>1500000</v>
       </c>
       <c r="E229" s="8" t="n">
-        <v>0.25</v>
+        <v>0.2059</v>
       </c>
       <c r="F229" s="7" t="n">
-        <v>47.5</v>
+        <v>57.52</v>
       </c>
       <c r="G229" s="7" t="n">
-        <v>49.58</v>
+        <v>1889.7</v>
       </c>
       <c r="H229" s="7" t="n">
         <v>1.28</v>
       </c>
       <c r="I229" s="8" t="n">
-        <v>0.0295</v>
+        <v>0.0008</v>
       </c>
       <c r="J229" s="8" t="n">
-        <v>-0.05889999999999999</v>
+        <v>1.5318</v>
       </c>
       <c r="K229" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>Sağlık teknolojisi</t>
         </is>
       </c>
       <c r="L229" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM, BIST ANA, BIST İZMİR</t>
         </is>
       </c>
       <c r="M229" s="6" t="inlineStr"/>
@@ -10444,42 +10440,44 @@
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>PINSU</t>
+          <t>KLSYN</t>
         </is>
       </c>
       <c r="B230" s="3" t="n">
-        <v>12.22</v>
+        <v>11.31</v>
       </c>
       <c r="C230" s="4" t="n">
-        <v>-0.03700000000000001</v>
+        <v>-0.0275</v>
       </c>
       <c r="D230" s="5" t="n">
-        <v>5390000</v>
+        <v>11290000</v>
       </c>
       <c r="E230" s="4" t="n">
-        <v>0.3326</v>
+        <v>0.25</v>
       </c>
       <c r="F230" s="3" t="n">
-        <v>53.98</v>
+        <v>47.5</v>
       </c>
       <c r="G230" s="3" t="n">
-        <v>60.5</v>
+        <v>49.58</v>
       </c>
       <c r="H230" s="3" t="n">
         <v>1.28</v>
       </c>
       <c r="I230" s="4" t="n">
-        <v>0.0243</v>
-      </c>
-      <c r="J230" s="2" t="inlineStr"/>
+        <v>0.0295</v>
+      </c>
+      <c r="J230" s="4" t="n">
+        <v>-0.05889999999999999</v>
+      </c>
       <c r="K230" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="L230" s="2" t="inlineStr">
         <is>
-          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST ANA, BIST KURUMSAL YÖNETİM, BIST İZMİR</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
         </is>
       </c>
       <c r="M230" s="2" t="inlineStr"/>
@@ -10487,36 +10485,34 @@
     <row r="231">
       <c r="A231" s="6" t="inlineStr">
         <is>
-          <t>VAKKO</t>
+          <t>PINSU</t>
         </is>
       </c>
       <c r="B231" s="7" t="n">
-        <v>78.5</v>
+        <v>12.22</v>
       </c>
       <c r="C231" s="8" t="n">
-        <v>-0.0113</v>
+        <v>-0.03700000000000001</v>
       </c>
       <c r="D231" s="9" t="n">
-        <v>554650</v>
+        <v>5390000</v>
       </c>
       <c r="E231" s="8" t="n">
-        <v>0.1504</v>
+        <v>0.3326</v>
       </c>
       <c r="F231" s="7" t="n">
-        <v>41.46</v>
+        <v>53.98</v>
       </c>
       <c r="G231" s="7" t="n">
-        <v>219.83</v>
+        <v>60.5</v>
       </c>
       <c r="H231" s="7" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="I231" s="8" t="n">
-        <v>0.006500000000000001</v>
-      </c>
-      <c r="J231" s="8" t="n">
-        <v>328.5973</v>
-      </c>
+        <v>0.0243</v>
+      </c>
+      <c r="J231" s="6" t="inlineStr"/>
       <c r="K231" s="6" t="inlineStr">
         <is>
           <t>Dayanıklı olmayan tüketici ürünleri</t>
@@ -10524,7 +10520,7 @@
       </c>
       <c r="L231" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST KATILIM TEMETTU</t>
+          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST ANA, BIST KURUMSAL YÖNETİM, BIST İZMİR</t>
         </is>
       </c>
       <c r="M231" s="6" t="inlineStr"/>
@@ -10532,44 +10528,44 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>LIDFA</t>
+          <t>VAKKO</t>
         </is>
       </c>
       <c r="B232" s="3" t="n">
-        <v>3.41</v>
+        <v>78.5</v>
       </c>
       <c r="C232" s="4" t="n">
-        <v>-0.0858</v>
+        <v>-0.0113</v>
       </c>
       <c r="D232" s="5" t="n">
-        <v>13810000</v>
+        <v>554650</v>
       </c>
       <c r="E232" s="4" t="n">
-        <v>0.4208</v>
+        <v>0.1504</v>
       </c>
       <c r="F232" s="3" t="n">
-        <v>46.5</v>
+        <v>41.46</v>
       </c>
       <c r="G232" s="3" t="n">
-        <v>3.83</v>
+        <v>219.83</v>
       </c>
       <c r="H232" s="3" t="n">
         <v>1.29</v>
       </c>
       <c r="I232" s="4" t="n">
-        <v>0.4054</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="J232" s="4" t="n">
-        <v>0.2344</v>
+        <v>328.5973</v>
       </c>
       <c r="K232" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L232" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST FIN KIR FAKTÖRIZASYONU, BIST MALİ, BIST ANA, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST KATILIM TEMETTU</t>
         </is>
       </c>
       <c r="M232" s="2" t="inlineStr"/>
@@ -10577,42 +10573,44 @@
     <row r="233">
       <c r="A233" s="6" t="inlineStr">
         <is>
-          <t>BAKAB</t>
+          <t>LIDFA</t>
         </is>
       </c>
       <c r="B233" s="7" t="n">
-        <v>49.84</v>
+        <v>3.41</v>
       </c>
       <c r="C233" s="8" t="n">
-        <v>0.09970000000000001</v>
+        <v>-0.0858</v>
       </c>
       <c r="D233" s="9" t="n">
-        <v>662380</v>
+        <v>13810000</v>
       </c>
       <c r="E233" s="8" t="n">
-        <v>0.2133</v>
+        <v>0.4208</v>
       </c>
       <c r="F233" s="7" t="n">
-        <v>67.09</v>
-      </c>
-      <c r="G233" s="6" t="inlineStr"/>
+        <v>46.5</v>
+      </c>
+      <c r="G233" s="7" t="n">
+        <v>3.83</v>
+      </c>
       <c r="H233" s="7" t="n">
         <v>1.29</v>
       </c>
       <c r="I233" s="8" t="n">
-        <v>-0.0635</v>
+        <v>0.4054</v>
       </c>
       <c r="J233" s="8" t="n">
-        <v>-0.0447</v>
+        <v>0.2344</v>
       </c>
       <c r="K233" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L233" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST KATILIM TÜM, BIST ANA, BIST İZMİR</t>
+          <t>BIST TUM-100, BIST TÜM, BIST FIN KIR FAKTÖRIZASYONU, BIST MALİ, BIST ANA, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M233" s="6" t="inlineStr"/>
@@ -10620,44 +10618,42 @@
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>HALKB</t>
+          <t>BAKAB</t>
         </is>
       </c>
       <c r="B234" s="3" t="n">
-        <v>40.76</v>
+        <v>49.84</v>
       </c>
       <c r="C234" s="4" t="n">
-        <v>-0.001</v>
+        <v>0.09970000000000001</v>
       </c>
       <c r="D234" s="5" t="n">
-        <v>41260000</v>
+        <v>662380</v>
       </c>
       <c r="E234" s="4" t="n">
-        <v>0.0851</v>
+        <v>0.2133</v>
       </c>
       <c r="F234" s="3" t="n">
-        <v>55.97</v>
-      </c>
-      <c r="G234" s="3" t="n">
-        <v>9.69</v>
-      </c>
+        <v>67.09</v>
+      </c>
+      <c r="G234" s="2" t="inlineStr"/>
       <c r="H234" s="3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="I234" s="4" t="n">
-        <v>0.1513</v>
+        <v>-0.0635</v>
       </c>
       <c r="J234" s="4" t="n">
-        <v>0.3723</v>
+        <v>-0.0447</v>
       </c>
       <c r="K234" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L234" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST BANKA, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST LİKİT BANKA, BIST MALİ, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST 50-30, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST KATILIM TÜM, BIST ANA, BIST İZMİR</t>
         </is>
       </c>
       <c r="M234" s="2" t="inlineStr"/>
@@ -10665,44 +10661,44 @@
     <row r="235">
       <c r="A235" s="6" t="inlineStr">
         <is>
-          <t>DURKN</t>
+          <t>HALKB</t>
         </is>
       </c>
       <c r="B235" s="7" t="n">
-        <v>23.26</v>
+        <v>40.76</v>
       </c>
       <c r="C235" s="8" t="n">
-        <v>0.0759</v>
+        <v>-0.001</v>
       </c>
       <c r="D235" s="9" t="n">
-        <v>5650000</v>
+        <v>41260000</v>
       </c>
       <c r="E235" s="8" t="n">
-        <v>0.283</v>
+        <v>0.0851</v>
       </c>
       <c r="F235" s="7" t="n">
-        <v>65.2</v>
+        <v>55.97</v>
       </c>
       <c r="G235" s="7" t="n">
-        <v>25.27</v>
+        <v>9.69</v>
       </c>
       <c r="H235" s="7" t="n">
         <v>1.3</v>
       </c>
       <c r="I235" s="8" t="n">
-        <v>0.0595</v>
+        <v>0.1513</v>
       </c>
       <c r="J235" s="8" t="n">
-        <v>0.9056999999999999</v>
+        <v>0.3723</v>
       </c>
       <c r="K235" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L235" s="6" t="inlineStr">
         <is>
-          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST ANA, BIST ANKARA</t>
+          <t>BIST 100, BIST BANKA, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST LİKİT BANKA, BIST MALİ, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST SÜRDÜRÜLEBİLİRLİK, BIST KURUMSAL YÖNETİM, BIST 50-30, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
         </is>
       </c>
       <c r="M235" s="6" t="inlineStr"/>
@@ -10710,42 +10706,44 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>ECZYT</t>
+          <t>DURKN</t>
         </is>
       </c>
       <c r="B236" s="3" t="n">
-        <v>373</v>
+        <v>23.26</v>
       </c>
       <c r="C236" s="4" t="n">
-        <v>-0.01</v>
+        <v>0.0759</v>
       </c>
       <c r="D236" s="5" t="n">
-        <v>554310</v>
+        <v>5650000</v>
       </c>
       <c r="E236" s="4" t="n">
-        <v>0.1843</v>
+        <v>0.283</v>
       </c>
       <c r="F236" s="3" t="n">
-        <v>53.77</v>
-      </c>
-      <c r="G236" s="2" t="inlineStr"/>
+        <v>65.2</v>
+      </c>
+      <c r="G236" s="3" t="n">
+        <v>25.27</v>
+      </c>
       <c r="H236" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="I236" s="4" t="n">
-        <v>-0.0012</v>
+        <v>0.0595</v>
       </c>
       <c r="J236" s="4" t="n">
-        <v>-1.2026</v>
+        <v>0.9056999999999999</v>
       </c>
       <c r="K236" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L236" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST YILDIZ, BIST TEMETTU</t>
+          <t>BIST GIDA ICECEK, BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST ANA, BIST ANKARA</t>
         </is>
       </c>
       <c r="M236" s="2" t="inlineStr"/>
@@ -10753,44 +10751,42 @@
     <row r="237">
       <c r="A237" s="6" t="inlineStr">
         <is>
-          <t>MARBL</t>
+          <t>ECZYT</t>
         </is>
       </c>
       <c r="B237" s="7" t="n">
-        <v>13.59</v>
+        <v>373</v>
       </c>
       <c r="C237" s="8" t="n">
-        <v>-0.0251</v>
+        <v>-0.01</v>
       </c>
       <c r="D237" s="9" t="n">
-        <v>3380000</v>
+        <v>554310</v>
       </c>
       <c r="E237" s="8" t="n">
-        <v>0.2623</v>
+        <v>0.1843</v>
       </c>
       <c r="F237" s="7" t="n">
-        <v>52.49</v>
-      </c>
-      <c r="G237" s="7" t="n">
-        <v>2613.46</v>
-      </c>
+        <v>53.77</v>
+      </c>
+      <c r="G237" s="6" t="inlineStr"/>
       <c r="H237" s="7" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="I237" s="8" t="n">
-        <v>0.0005</v>
+        <v>-0.0012</v>
       </c>
       <c r="J237" s="8" t="n">
-        <v>-5.5053</v>
+        <v>-1.2026</v>
       </c>
       <c r="K237" s="6" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L237" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST YILDIZ, BIST TEMETTU</t>
         </is>
       </c>
       <c r="M237" s="6" t="inlineStr"/>
@@ -10798,44 +10794,44 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>OYYAT</t>
+          <t>MARBL</t>
         </is>
       </c>
       <c r="B238" s="3" t="n">
-        <v>53.35</v>
+        <v>13.59</v>
       </c>
       <c r="C238" s="4" t="n">
-        <v>-0.022</v>
+        <v>-0.0251</v>
       </c>
       <c r="D238" s="5" t="n">
-        <v>645070</v>
+        <v>3380000</v>
       </c>
       <c r="E238" s="4" t="n">
-        <v>0.3035</v>
+        <v>0.2623</v>
       </c>
       <c r="F238" s="3" t="n">
-        <v>41.66</v>
+        <v>52.49</v>
       </c>
       <c r="G238" s="3" t="n">
-        <v>7.04</v>
+        <v>2613.46</v>
       </c>
       <c r="H238" s="3" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="I238" s="4" t="n">
-        <v>0.231</v>
+        <v>0.0005</v>
       </c>
       <c r="J238" s="4" t="n">
-        <v>13.7151</v>
+        <v>-5.5053</v>
       </c>
       <c r="K238" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="L238" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST MALİ, BIST ARACI KURUMLAR, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M238" s="2" t="inlineStr"/>
@@ -19365,42 +19361,44 @@
     <row r="435">
       <c r="A435" s="6" t="inlineStr">
         <is>
-          <t>KARTN</t>
+          <t>GENIL</t>
         </is>
       </c>
       <c r="B435" s="7" t="n">
-        <v>119</v>
+        <v>9.44</v>
       </c>
       <c r="C435" s="8" t="n">
-        <v>-0.0426</v>
+        <v>-0.0021</v>
       </c>
       <c r="D435" s="9" t="n">
-        <v>1690000</v>
+        <v>141000000</v>
       </c>
       <c r="E435" s="8" t="n">
-        <v>0.2186</v>
+        <v>0.2412</v>
       </c>
       <c r="F435" s="7" t="n">
-        <v>65.11</v>
-      </c>
-      <c r="G435" s="6" t="inlineStr"/>
+        <v>48.63</v>
+      </c>
+      <c r="G435" s="7" t="n">
+        <v>51.75</v>
+      </c>
       <c r="H435" s="7" t="n">
         <v>3.61</v>
       </c>
       <c r="I435" s="8" t="n">
-        <v>-0.4183</v>
+        <v>0.0815</v>
       </c>
       <c r="J435" s="8" t="n">
-        <v>-1.6177</v>
+        <v>1.4915</v>
       </c>
       <c r="K435" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Sağlık teknolojisi</t>
         </is>
       </c>
       <c r="L435" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST ANA, BIST KOCAELI</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU, BIST KATILIM 50, BIST KATILIM 30, BIST KATILIM TEMETTU, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
         </is>
       </c>
       <c r="M435" s="6" t="inlineStr"/>
@@ -19408,44 +19406,42 @@
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>EUPWR</t>
+          <t>KARTN</t>
         </is>
       </c>
       <c r="B436" s="3" t="n">
-        <v>58.8</v>
+        <v>119</v>
       </c>
       <c r="C436" s="4" t="n">
-        <v>0.0199</v>
+        <v>-0.0426</v>
       </c>
       <c r="D436" s="5" t="n">
-        <v>37400000</v>
+        <v>1690000</v>
       </c>
       <c r="E436" s="4" t="n">
-        <v>0.3025</v>
+        <v>0.2186</v>
       </c>
       <c r="F436" s="3" t="n">
-        <v>73.09999999999999</v>
-      </c>
-      <c r="G436" s="3" t="n">
-        <v>67.7</v>
-      </c>
+        <v>65.11</v>
+      </c>
+      <c r="G436" s="2" t="inlineStr"/>
       <c r="H436" s="3" t="n">
-        <v>3.68</v>
+        <v>3.61</v>
       </c>
       <c r="I436" s="4" t="n">
-        <v>0.06320000000000001</v>
+        <v>-0.4183</v>
       </c>
       <c r="J436" s="4" t="n">
-        <v>-1.0812</v>
+        <v>-1.6177</v>
       </c>
       <c r="K436" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L436" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M436" s="2" t="inlineStr"/>
@@ -19453,44 +19449,44 @@
     <row r="437">
       <c r="A437" s="6" t="inlineStr">
         <is>
-          <t>EGEGY</t>
+          <t>EUPWR</t>
         </is>
       </c>
       <c r="B437" s="7" t="n">
-        <v>32.2</v>
+        <v>58.8</v>
       </c>
       <c r="C437" s="8" t="n">
-        <v>0.0255</v>
+        <v>0.0199</v>
       </c>
       <c r="D437" s="9" t="n">
-        <v>4710000</v>
+        <v>37400000</v>
       </c>
       <c r="E437" s="8" t="n">
-        <v>0.306</v>
+        <v>0.3025</v>
       </c>
       <c r="F437" s="7" t="n">
-        <v>58.84</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="G437" s="7" t="n">
-        <v>8.24</v>
+        <v>67.7</v>
       </c>
       <c r="H437" s="7" t="n">
-        <v>3.75</v>
+        <v>3.68</v>
       </c>
       <c r="I437" s="8" t="n">
-        <v>0.8473999999999999</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="J437" s="8" t="n">
-        <v>5.585199999999999</v>
+        <v>-1.0812</v>
       </c>
       <c r="K437" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L437" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST ANA</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST SINAI, BIST TÜM, BIST METAL ESYA MAKİNA, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
         </is>
       </c>
       <c r="M437" s="6" t="inlineStr"/>
@@ -19498,44 +19494,44 @@
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
         <is>
-          <t>ARDYZ</t>
+          <t>EGEGY</t>
         </is>
       </c>
       <c r="B438" s="3" t="n">
-        <v>59</v>
+        <v>32.2</v>
       </c>
       <c r="C438" s="4" t="n">
-        <v>0.0051</v>
+        <v>0.0255</v>
       </c>
       <c r="D438" s="5" t="n">
-        <v>6860000</v>
+        <v>4710000</v>
       </c>
       <c r="E438" s="4" t="n">
-        <v>0.3949</v>
+        <v>0.306</v>
       </c>
       <c r="F438" s="3" t="n">
-        <v>78.13</v>
+        <v>58.84</v>
       </c>
       <c r="G438" s="3" t="n">
-        <v>28.18</v>
+        <v>8.24</v>
       </c>
       <c r="H438" s="3" t="n">
-        <v>3.77</v>
+        <v>3.75</v>
       </c>
       <c r="I438" s="4" t="n">
-        <v>0.1333</v>
+        <v>0.8473999999999999</v>
       </c>
       <c r="J438" s="4" t="n">
-        <v>6.844600000000001</v>
+        <v>5.585199999999999</v>
       </c>
       <c r="K438" s="2" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L438" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST ANA</t>
         </is>
       </c>
       <c r="M438" s="2" t="inlineStr"/>
@@ -19543,42 +19539,44 @@
     <row r="439">
       <c r="A439" s="6" t="inlineStr">
         <is>
-          <t>ENSRI</t>
+          <t>ARDYZ</t>
         </is>
       </c>
       <c r="B439" s="7" t="n">
-        <v>10.02</v>
+        <v>59</v>
       </c>
       <c r="C439" s="8" t="n">
-        <v>-0.005</v>
+        <v>0.0051</v>
       </c>
       <c r="D439" s="9" t="n">
-        <v>95770000</v>
+        <v>6860000</v>
       </c>
       <c r="E439" s="8" t="n">
-        <v>0.4329</v>
+        <v>0.3949</v>
       </c>
       <c r="F439" s="7" t="n">
-        <v>22.41</v>
-      </c>
-      <c r="G439" s="6" t="inlineStr"/>
+        <v>78.13</v>
+      </c>
+      <c r="G439" s="7" t="n">
+        <v>28.18</v>
+      </c>
       <c r="H439" s="7" t="n">
-        <v>3.87</v>
+        <v>3.77</v>
       </c>
       <c r="I439" s="8" t="n">
-        <v>-0.0555</v>
+        <v>0.1333</v>
       </c>
       <c r="J439" s="8" t="n">
-        <v>-10.8224</v>
+        <v>6.844600000000001</v>
       </c>
       <c r="K439" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="L439" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST ANA, BIST TEKİRDAĞ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
         </is>
       </c>
       <c r="M439" s="6" t="inlineStr"/>
@@ -19586,33 +19584,33 @@
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>IZINV</t>
+          <t>ENSRI</t>
         </is>
       </c>
       <c r="B440" s="3" t="n">
-        <v>79.40000000000001</v>
+        <v>10.02</v>
       </c>
       <c r="C440" s="4" t="n">
-        <v>-0.0038</v>
+        <v>-0.005</v>
       </c>
       <c r="D440" s="5" t="n">
-        <v>1440000</v>
+        <v>95770000</v>
       </c>
       <c r="E440" s="4" t="n">
-        <v>0.7040999999999999</v>
+        <v>0.4329</v>
       </c>
       <c r="F440" s="3" t="n">
-        <v>65.22</v>
+        <v>22.41</v>
       </c>
       <c r="G440" s="2" t="inlineStr"/>
       <c r="H440" s="3" t="n">
-        <v>3.89</v>
+        <v>3.87</v>
       </c>
       <c r="I440" s="4" t="n">
-        <v>-0.1552</v>
+        <v>-0.0555</v>
       </c>
       <c r="J440" s="4" t="n">
-        <v>-0.45</v>
+        <v>-10.8224</v>
       </c>
       <c r="K440" s="2" t="inlineStr">
         <is>
@@ -19621,7 +19619,7 @@
       </c>
       <c r="L440" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST KOBİ SANAYİ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TEKSTİL DERİ, BIST ANA, BIST TEKİRDAĞ</t>
         </is>
       </c>
       <c r="M440" s="2" t="inlineStr"/>
@@ -19629,38 +19627,42 @@
     <row r="441">
       <c r="A441" s="6" t="inlineStr">
         <is>
-          <t>ZERGY</t>
+          <t>IZINV</t>
         </is>
       </c>
       <c r="B441" s="7" t="n">
-        <v>22</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="C441" s="8" t="n">
-        <v>0.1</v>
+        <v>-0.0038</v>
       </c>
       <c r="D441" s="9" t="n">
-        <v>17600000</v>
+        <v>1440000</v>
       </c>
       <c r="E441" s="8" t="n">
-        <v>0.1865</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="F441" s="7" t="n">
-        <v>54.76</v>
+        <v>65.22</v>
       </c>
       <c r="G441" s="6" t="inlineStr"/>
       <c r="H441" s="7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="I441" s="6" t="inlineStr"/>
-      <c r="J441" s="6" t="inlineStr"/>
+        <v>3.89</v>
+      </c>
+      <c r="I441" s="8" t="n">
+        <v>-0.1552</v>
+      </c>
+      <c r="J441" s="8" t="n">
+        <v>-0.45</v>
+      </c>
       <c r="K441" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L441" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST KOBİ SANAYİ</t>
         </is>
       </c>
       <c r="M441" s="6" t="inlineStr"/>
@@ -19668,42 +19670,38 @@
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
         <is>
-          <t>ALKA</t>
+          <t>ZERGY</t>
         </is>
       </c>
       <c r="B442" s="3" t="n">
-        <v>11.3</v>
+        <v>22</v>
       </c>
       <c r="C442" s="4" t="n">
-        <v>-0.0208</v>
+        <v>0.1</v>
       </c>
       <c r="D442" s="5" t="n">
-        <v>7320000</v>
+        <v>17600000</v>
       </c>
       <c r="E442" s="4" t="n">
-        <v>0.1937</v>
+        <v>0.1865</v>
       </c>
       <c r="F442" s="3" t="n">
-        <v>47.71</v>
+        <v>54.76</v>
       </c>
       <c r="G442" s="2" t="inlineStr"/>
       <c r="H442" s="3" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="I442" s="4" t="n">
-        <v>-0.0556</v>
-      </c>
-      <c r="J442" s="4" t="n">
-        <v>-7.241000000000001</v>
-      </c>
+        <v>3.95</v>
+      </c>
+      <c r="I442" s="2" t="inlineStr"/>
+      <c r="J442" s="2" t="inlineStr"/>
       <c r="K442" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L442" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST KATILIM TÜM, BIST ANA, BIST İZMİR</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M442" s="2" t="inlineStr"/>
@@ -19711,44 +19709,42 @@
     <row r="443">
       <c r="A443" s="6" t="inlineStr">
         <is>
-          <t>ATATP</t>
+          <t>ALKA</t>
         </is>
       </c>
       <c r="B443" s="7" t="n">
-        <v>188.1</v>
+        <v>11.3</v>
       </c>
       <c r="C443" s="8" t="n">
-        <v>0.1</v>
+        <v>-0.0208</v>
       </c>
       <c r="D443" s="9" t="n">
-        <v>1680000</v>
+        <v>7320000</v>
       </c>
       <c r="E443" s="8" t="n">
-        <v>0.0158</v>
+        <v>0.1937</v>
       </c>
       <c r="F443" s="7" t="n">
-        <v>78.51000000000001</v>
-      </c>
-      <c r="G443" s="7" t="n">
-        <v>2.5</v>
-      </c>
+        <v>47.71</v>
+      </c>
+      <c r="G443" s="6" t="inlineStr"/>
       <c r="H443" s="7" t="n">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="I443" s="8" t="n">
-        <v>0.6533</v>
+        <v>-0.0556</v>
       </c>
       <c r="J443" s="8" t="n">
-        <v>-0.1442</v>
+        <v>-7.241000000000001</v>
       </c>
       <c r="K443" s="6" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L443" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST KATILIM TÜM, BIST ANA, BIST İZMİR</t>
         </is>
       </c>
       <c r="M443" s="6" t="inlineStr"/>
@@ -19756,42 +19752,44 @@
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
         <is>
-          <t>ALTNY</t>
+          <t>ATATP</t>
         </is>
       </c>
       <c r="B444" s="3" t="n">
-        <v>18.5</v>
+        <v>188.1</v>
       </c>
       <c r="C444" s="4" t="n">
-        <v>-0.0449</v>
+        <v>0.1</v>
       </c>
       <c r="D444" s="5" t="n">
-        <v>45050000</v>
+        <v>1680000</v>
       </c>
       <c r="E444" s="4" t="n">
-        <v>0.3999</v>
+        <v>0.0158</v>
       </c>
       <c r="F444" s="3" t="n">
-        <v>67.31</v>
+        <v>78.51000000000001</v>
       </c>
       <c r="G444" s="3" t="n">
-        <v>75.91</v>
+        <v>2.5</v>
       </c>
       <c r="H444" s="3" t="n">
         <v>4</v>
       </c>
       <c r="I444" s="4" t="n">
-        <v>-0.0039</v>
-      </c>
-      <c r="J444" s="2" t="inlineStr"/>
+        <v>0.6533</v>
+      </c>
+      <c r="J444" s="4" t="n">
+        <v>-0.1442</v>
+      </c>
       <c r="K444" s="2" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="L444" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST TEKNOLOJİ, BIST HALKA ARZ, BIST İSTANBUL, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM 30, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
         </is>
       </c>
       <c r="M444" s="2" t="inlineStr"/>
@@ -19799,42 +19797,42 @@
     <row r="445">
       <c r="A445" s="6" t="inlineStr">
         <is>
-          <t>BURCE</t>
+          <t>ALTNY</t>
         </is>
       </c>
       <c r="B445" s="7" t="n">
-        <v>52.5</v>
+        <v>18.5</v>
       </c>
       <c r="C445" s="8" t="n">
-        <v>-0.0331</v>
+        <v>-0.0449</v>
       </c>
       <c r="D445" s="9" t="n">
-        <v>5180000</v>
+        <v>45050000</v>
       </c>
       <c r="E445" s="8" t="n">
-        <v>0.5275</v>
+        <v>0.3999</v>
       </c>
       <c r="F445" s="7" t="n">
-        <v>51.08</v>
-      </c>
-      <c r="G445" s="6" t="inlineStr"/>
+        <v>67.31</v>
+      </c>
+      <c r="G445" s="7" t="n">
+        <v>75.91</v>
+      </c>
       <c r="H445" s="7" t="n">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="I445" s="8" t="n">
-        <v>-0.1171</v>
-      </c>
-      <c r="J445" s="8" t="n">
-        <v>-1.2976</v>
-      </c>
+        <v>-0.0039</v>
+      </c>
+      <c r="J445" s="6" t="inlineStr"/>
       <c r="K445" s="6" t="inlineStr">
         <is>
-          <t>Enerji-dışı mineraller</t>
+          <t>Elektronik teknoloji</t>
         </is>
       </c>
       <c r="L445" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST KATILIM TÜM, BIST ANA, BIST BURSA</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST TEKNOLOJİ, BIST HALKA ARZ, BIST İSTANBUL, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM 30, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
         </is>
       </c>
       <c r="M445" s="6" t="inlineStr"/>
@@ -19842,42 +19840,42 @@
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
         <is>
-          <t>INVES</t>
+          <t>BURCE</t>
         </is>
       </c>
       <c r="B446" s="3" t="n">
-        <v>580</v>
+        <v>52.5</v>
       </c>
       <c r="C446" s="4" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.0331</v>
       </c>
       <c r="D446" s="5" t="n">
-        <v>123240</v>
+        <v>5180000</v>
       </c>
       <c r="E446" s="4" t="n">
-        <v>0.2</v>
+        <v>0.5275</v>
       </c>
       <c r="F446" s="3" t="n">
-        <v>69.88</v>
-      </c>
-      <c r="G446" s="3" t="n">
-        <v>43.37</v>
-      </c>
+        <v>51.08</v>
+      </c>
+      <c r="G446" s="2" t="inlineStr"/>
       <c r="H446" s="3" t="n">
-        <v>4.03</v>
+        <v>4.01</v>
       </c>
       <c r="I446" s="4" t="n">
-        <v>0.1111</v>
-      </c>
-      <c r="J446" s="2" t="inlineStr"/>
+        <v>-0.1171</v>
+      </c>
+      <c r="J446" s="4" t="n">
+        <v>-1.2976</v>
+      </c>
       <c r="K446" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Enerji-dışı mineraller</t>
         </is>
       </c>
       <c r="L446" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST KATILIM TÜM, BIST ANA, BIST BURSA</t>
         </is>
       </c>
       <c r="M446" s="2" t="inlineStr"/>
@@ -19885,44 +19883,42 @@
     <row r="447">
       <c r="A447" s="6" t="inlineStr">
         <is>
-          <t>TCKRC</t>
+          <t>INVES</t>
         </is>
       </c>
       <c r="B447" s="7" t="n">
-        <v>125</v>
+        <v>580</v>
       </c>
       <c r="C447" s="8" t="n">
-        <v>0.06559999999999999</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="D447" s="9" t="n">
-        <v>6160000</v>
+        <v>123240</v>
       </c>
       <c r="E447" s="8" t="n">
-        <v>0.3229</v>
+        <v>0.2</v>
       </c>
       <c r="F447" s="7" t="n">
-        <v>79.84999999999999</v>
+        <v>69.88</v>
       </c>
       <c r="G447" s="7" t="n">
-        <v>17.6</v>
+        <v>43.37</v>
       </c>
       <c r="H447" s="7" t="n">
-        <v>4.05</v>
+        <v>4.03</v>
       </c>
       <c r="I447" s="8" t="n">
-        <v>0.2909</v>
-      </c>
-      <c r="J447" s="8" t="n">
-        <v>2.7171</v>
-      </c>
+        <v>0.1111</v>
+      </c>
+      <c r="J447" s="6" t="inlineStr"/>
       <c r="K447" s="6" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L447" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST HALKA ARZ, BIST YILDIZ, BIST BURSA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M447" s="6" t="inlineStr"/>
@@ -19930,42 +19926,44 @@
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
         <is>
-          <t>OTTO</t>
+          <t>TCKRC</t>
         </is>
       </c>
       <c r="B448" s="3" t="n">
-        <v>301.75</v>
+        <v>125</v>
       </c>
       <c r="C448" s="4" t="n">
-        <v>-0.0203</v>
+        <v>0.06559999999999999</v>
       </c>
       <c r="D448" s="5" t="n">
-        <v>453370</v>
+        <v>6160000</v>
       </c>
       <c r="E448" s="4" t="n">
-        <v>0.3623</v>
+        <v>0.3229</v>
       </c>
       <c r="F448" s="3" t="n">
-        <v>39.92</v>
-      </c>
-      <c r="G448" s="2" t="inlineStr"/>
+        <v>79.84999999999999</v>
+      </c>
+      <c r="G448" s="3" t="n">
+        <v>17.6</v>
+      </c>
       <c r="H448" s="3" t="n">
         <v>4.05</v>
       </c>
       <c r="I448" s="4" t="n">
-        <v>-0.0108</v>
+        <v>0.2909</v>
       </c>
       <c r="J448" s="4" t="n">
-        <v>-0.3881</v>
+        <v>2.7171</v>
       </c>
       <c r="K448" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L448" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST METAL ANA, BIST HALKA ARZ, BIST YILDIZ, BIST BURSA</t>
         </is>
       </c>
       <c r="M448" s="2" t="inlineStr"/>
@@ -19973,42 +19971,42 @@
     <row r="449">
       <c r="A449" s="6" t="inlineStr">
         <is>
-          <t>TATEN</t>
+          <t>OTTO</t>
         </is>
       </c>
       <c r="B449" s="7" t="n">
-        <v>19.5</v>
+        <v>301.75</v>
       </c>
       <c r="C449" s="8" t="n">
-        <v>0.0762</v>
+        <v>-0.0203</v>
       </c>
       <c r="D449" s="9" t="n">
-        <v>83450000</v>
+        <v>453370</v>
       </c>
       <c r="E449" s="8" t="n">
-        <v>0.9165000000000001</v>
+        <v>0.3623</v>
       </c>
       <c r="F449" s="7" t="n">
-        <v>80.86</v>
+        <v>39.92</v>
       </c>
       <c r="G449" s="6" t="inlineStr"/>
       <c r="H449" s="7" t="n">
-        <v>4.07</v>
+        <v>4.05</v>
       </c>
       <c r="I449" s="8" t="n">
-        <v>-0.0159</v>
+        <v>-0.0108</v>
       </c>
       <c r="J449" s="8" t="n">
-        <v>-0.9540000000000001</v>
+        <v>-0.3881</v>
       </c>
       <c r="K449" s="6" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L449" s="6" t="inlineStr">
         <is>
-          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST YILDIZ, BIST BALIKESİR</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST ANA</t>
         </is>
       </c>
       <c r="M449" s="6" t="inlineStr"/>
@@ -20016,42 +20014,42 @@
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
         <is>
-          <t>TARKM</t>
+          <t>TATEN</t>
         </is>
       </c>
       <c r="B450" s="3" t="n">
-        <v>485</v>
+        <v>19.5</v>
       </c>
       <c r="C450" s="4" t="n">
-        <v>-0.0036</v>
+        <v>0.0762</v>
       </c>
       <c r="D450" s="5" t="n">
-        <v>530110</v>
+        <v>83450000</v>
       </c>
       <c r="E450" s="4" t="n">
-        <v>0.2381</v>
+        <v>0.9165000000000001</v>
       </c>
       <c r="F450" s="3" t="n">
-        <v>68.59999999999999</v>
+        <v>80.86</v>
       </c>
       <c r="G450" s="2" t="inlineStr"/>
       <c r="H450" s="3" t="n">
         <v>4.07</v>
       </c>
       <c r="I450" s="4" t="n">
-        <v>-0.0599</v>
+        <v>-0.0159</v>
       </c>
       <c r="J450" s="4" t="n">
-        <v>-44.8491</v>
+        <v>-0.9540000000000001</v>
       </c>
       <c r="K450" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="L450" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST MANİSA</t>
+          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST YILDIZ, BIST BALIKESİR</t>
         </is>
       </c>
       <c r="M450" s="2" t="inlineStr"/>
@@ -20059,44 +20057,42 @@
     <row r="451">
       <c r="A451" s="6" t="inlineStr">
         <is>
-          <t>GENIL</t>
+          <t>TARKM</t>
         </is>
       </c>
       <c r="B451" s="7" t="n">
-        <v>9.44</v>
+        <v>485</v>
       </c>
       <c r="C451" s="8" t="n">
-        <v>-0.0021</v>
+        <v>-0.0036</v>
       </c>
       <c r="D451" s="9" t="n">
-        <v>141000000</v>
+        <v>530110</v>
       </c>
       <c r="E451" s="8" t="n">
-        <v>0.2412</v>
+        <v>0.2381</v>
       </c>
       <c r="F451" s="7" t="n">
-        <v>48.63</v>
-      </c>
-      <c r="G451" s="7" t="n">
-        <v>55.53</v>
-      </c>
+        <v>68.59999999999999</v>
+      </c>
+      <c r="G451" s="6" t="inlineStr"/>
       <c r="H451" s="7" t="n">
-        <v>4.1</v>
+        <v>4.07</v>
       </c>
       <c r="I451" s="8" t="n">
-        <v>0.0866</v>
+        <v>-0.0599</v>
       </c>
       <c r="J451" s="8" t="n">
-        <v>-0.3022</v>
+        <v>-44.8491</v>
       </c>
       <c r="K451" s="6" t="inlineStr">
         <is>
-          <t>Sağlık teknolojisi</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L451" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU, BIST KATILIM 50, BIST KATILIM 30, BIST KATILIM TEMETTU, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM 100, BIST KATILIM TÜM, BIST ANA, BIST MANİSA</t>
         </is>
       </c>
       <c r="M451" s="6" t="inlineStr"/>
@@ -24586,120 +24582,122 @@
     <row r="556">
       <c r="A556" s="2" t="inlineStr">
         <is>
-          <t>DIRIT</t>
+          <t>KTLEV</t>
         </is>
       </c>
       <c r="B556" s="3" t="n">
-        <v>28.1</v>
+        <v>121.3</v>
       </c>
       <c r="C556" s="4" t="n">
-        <v>-0.0106</v>
+        <v>0.0185</v>
       </c>
       <c r="D556" s="5" t="n">
-        <v>66130</v>
-      </c>
-      <c r="E556" s="2" t="inlineStr"/>
+        <v>31940000</v>
+      </c>
+      <c r="E556" s="4" t="n">
+        <v>0.2784</v>
+      </c>
       <c r="F556" s="3" t="n">
-        <v>51.99</v>
-      </c>
-      <c r="G556" s="2" t="inlineStr"/>
+        <v>92.09</v>
+      </c>
+      <c r="G556" s="3" t="n">
+        <v>23.09</v>
+      </c>
       <c r="H556" s="3" t="n">
-        <v>17.4</v>
+        <v>17.02</v>
       </c>
       <c r="I556" s="4" t="n">
-        <v>-2.156</v>
+        <v>1.1579</v>
       </c>
       <c r="J556" s="4" t="n">
-        <v>-67.1895</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="K556" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L556" s="2" t="inlineStr"/>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L556" s="2" t="inlineStr">
+        <is>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST MALİ, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU, BIST KATILIM 50, BIST KATILIM 30, BIST KATILIM TEMETTU, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
+        </is>
+      </c>
       <c r="M556" s="2" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" s="6" t="inlineStr">
         <is>
-          <t>VKFYO</t>
+          <t>DIRIT</t>
         </is>
       </c>
       <c r="B557" s="7" t="n">
-        <v>33.94</v>
+        <v>28.1</v>
       </c>
       <c r="C557" s="8" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0106</v>
       </c>
       <c r="D557" s="9" t="n">
-        <v>390590</v>
+        <v>66130</v>
       </c>
       <c r="E557" s="6" t="inlineStr"/>
       <c r="F557" s="7" t="n">
-        <v>49.49</v>
+        <v>51.99</v>
       </c>
       <c r="G557" s="6" t="inlineStr"/>
       <c r="H557" s="7" t="n">
-        <v>18.4</v>
+        <v>17.4</v>
       </c>
       <c r="I557" s="8" t="n">
-        <v>-0.3087</v>
+        <v>-2.156</v>
       </c>
       <c r="J557" s="8" t="n">
-        <v>0.4908</v>
+        <v>-67.1895</v>
       </c>
       <c r="K557" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L557" s="6" t="inlineStr">
-        <is>
-          <t>BIST MENKUL KIYM YO</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L557" s="6" t="inlineStr"/>
       <c r="M557" s="6" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" s="2" t="inlineStr">
         <is>
-          <t>VKING</t>
+          <t>VKFYO</t>
         </is>
       </c>
       <c r="B558" s="3" t="n">
-        <v>26.88</v>
+        <v>33.94</v>
       </c>
       <c r="C558" s="4" t="n">
-        <v>-0.0441</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="D558" s="5" t="n">
-        <v>933460</v>
-      </c>
-      <c r="E558" s="4" t="n">
-        <v>0.9698</v>
-      </c>
+        <v>390590</v>
+      </c>
+      <c r="E558" s="2" t="inlineStr"/>
       <c r="F558" s="3" t="n">
-        <v>49.06</v>
+        <v>49.49</v>
       </c>
       <c r="G558" s="2" t="inlineStr"/>
       <c r="H558" s="3" t="n">
-        <v>18.77</v>
+        <v>18.4</v>
       </c>
       <c r="I558" s="4" t="n">
-        <v>-19.6981</v>
+        <v>-0.3087</v>
       </c>
       <c r="J558" s="4" t="n">
-        <v>-0.7162999999999999</v>
+        <v>0.4908</v>
       </c>
       <c r="K558" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L558" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST ANA, BIST İZMİR</t>
+          <t>BIST MENKUL KIYM YO</t>
         </is>
       </c>
       <c r="M558" s="2" t="inlineStr"/>
@@ -24707,44 +24705,42 @@
     <row r="559">
       <c r="A559" s="6" t="inlineStr">
         <is>
-          <t>ONCSM</t>
+          <t>VKING</t>
         </is>
       </c>
       <c r="B559" s="7" t="n">
-        <v>325</v>
+        <v>26.88</v>
       </c>
       <c r="C559" s="8" t="n">
-        <v>0.0442</v>
+        <v>-0.0441</v>
       </c>
       <c r="D559" s="9" t="n">
-        <v>877640</v>
+        <v>933460</v>
       </c>
       <c r="E559" s="8" t="n">
-        <v>0.3512</v>
+        <v>0.9698</v>
       </c>
       <c r="F559" s="7" t="n">
-        <v>72.22</v>
-      </c>
-      <c r="G559" s="7" t="n">
-        <v>157.13</v>
-      </c>
+        <v>49.06</v>
+      </c>
+      <c r="G559" s="6" t="inlineStr"/>
       <c r="H559" s="7" t="n">
-        <v>19.04</v>
+        <v>18.77</v>
       </c>
       <c r="I559" s="8" t="n">
-        <v>0.1448</v>
+        <v>-19.6981</v>
       </c>
       <c r="J559" s="8" t="n">
-        <v>0.4836</v>
+        <v>-0.7162999999999999</v>
       </c>
       <c r="K559" s="6" t="inlineStr">
         <is>
-          <t>Sağlık teknolojisi</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L559" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM, BIST ANA, BIST KOBİ SANAYİ, BIST ANKARA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST ORMAN KAĞIT BASIM, BIST ANA, BIST İZMİR</t>
         </is>
       </c>
       <c r="M559" s="6" t="inlineStr"/>
@@ -24752,44 +24748,44 @@
     <row r="560">
       <c r="A560" s="2" t="inlineStr">
         <is>
-          <t>RALYH</t>
+          <t>ONCSM</t>
         </is>
       </c>
       <c r="B560" s="3" t="n">
-        <v>360</v>
+        <v>325</v>
       </c>
       <c r="C560" s="4" t="n">
-        <v>-0.0716</v>
+        <v>0.0442</v>
       </c>
       <c r="D560" s="5" t="n">
-        <v>1880000</v>
+        <v>877640</v>
       </c>
       <c r="E560" s="4" t="n">
-        <v>0.3721</v>
+        <v>0.3512</v>
       </c>
       <c r="F560" s="3" t="n">
-        <v>63.13</v>
+        <v>72.22</v>
       </c>
       <c r="G560" s="3" t="n">
-        <v>51.62</v>
+        <v>157.13</v>
       </c>
       <c r="H560" s="3" t="n">
-        <v>19.18</v>
+        <v>19.04</v>
       </c>
       <c r="I560" s="4" t="n">
-        <v>0.4916</v>
+        <v>0.1448</v>
       </c>
       <c r="J560" s="4" t="n">
-        <v>2.6125</v>
+        <v>0.4836</v>
       </c>
       <c r="K560" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Sağlık teknolojisi</t>
         </is>
       </c>
       <c r="L560" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST KATILIM TÜM, BIST ANA, BIST KOBİ SANAYİ, BIST ANKARA</t>
         </is>
       </c>
       <c r="M560" s="2" t="inlineStr"/>
@@ -24797,124 +24793,126 @@
     <row r="561">
       <c r="A561" s="6" t="inlineStr">
         <is>
-          <t>KENT</t>
+          <t>RALYH</t>
         </is>
       </c>
       <c r="B561" s="7" t="n">
-        <v>405</v>
+        <v>360</v>
       </c>
       <c r="C561" s="8" t="n">
-        <v>-0.0264</v>
+        <v>-0.0716</v>
       </c>
       <c r="D561" s="9" t="n">
-        <v>7340</v>
+        <v>1880000</v>
       </c>
       <c r="E561" s="8" t="n">
-        <v>0.0059</v>
+        <v>0.3721</v>
       </c>
       <c r="F561" s="7" t="n">
-        <v>42.45</v>
-      </c>
-      <c r="G561" s="6" t="inlineStr"/>
+        <v>63.13</v>
+      </c>
+      <c r="G561" s="7" t="n">
+        <v>51.62</v>
+      </c>
       <c r="H561" s="7" t="n">
-        <v>19.6</v>
+        <v>19.18</v>
       </c>
       <c r="I561" s="8" t="n">
-        <v>-0.0998</v>
+        <v>0.4916</v>
       </c>
       <c r="J561" s="8" t="n">
-        <v>-4.3494</v>
+        <v>2.6125</v>
       </c>
       <c r="K561" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
-        </is>
-      </c>
-      <c r="L561" s="6" t="inlineStr"/>
+          <t>Endüstriyel hizmetler</t>
+        </is>
+      </c>
+      <c r="L561" s="6" t="inlineStr">
+        <is>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
+        </is>
+      </c>
       <c r="M561" s="6" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" s="2" t="inlineStr">
         <is>
-          <t>MRSHL</t>
-        </is>
-      </c>
-      <c r="B562" s="5" t="n">
-        <v>1585</v>
+          <t>KENT</t>
+        </is>
+      </c>
+      <c r="B562" s="3" t="n">
+        <v>405</v>
       </c>
       <c r="C562" s="4" t="n">
-        <v>-0.0258</v>
+        <v>-0.0264</v>
       </c>
       <c r="D562" s="5" t="n">
-        <v>31910</v>
+        <v>7340</v>
       </c>
       <c r="E562" s="4" t="n">
-        <v>0.0639</v>
+        <v>0.0059</v>
       </c>
       <c r="F562" s="3" t="n">
-        <v>55.61</v>
+        <v>42.45</v>
       </c>
       <c r="G562" s="2" t="inlineStr"/>
       <c r="H562" s="3" t="n">
-        <v>19.82</v>
+        <v>19.6</v>
       </c>
       <c r="I562" s="4" t="n">
-        <v>-0.3366</v>
+        <v>-0.0998</v>
       </c>
       <c r="J562" s="4" t="n">
-        <v>0.5811999999999999</v>
+        <v>-4.3494</v>
       </c>
       <c r="K562" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L562" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
-        </is>
-      </c>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
+      <c r="L562" s="2" t="inlineStr"/>
       <c r="M562" s="2" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" s="6" t="inlineStr">
         <is>
-          <t>COSMO</t>
-        </is>
-      </c>
-      <c r="B563" s="7" t="n">
-        <v>219.9</v>
+          <t>MRSHL</t>
+        </is>
+      </c>
+      <c r="B563" s="9" t="n">
+        <v>1585</v>
       </c>
       <c r="C563" s="8" t="n">
-        <v>0.08380000000000001</v>
+        <v>-0.0258</v>
       </c>
       <c r="D563" s="9" t="n">
-        <v>76070</v>
+        <v>31910</v>
       </c>
       <c r="E563" s="8" t="n">
-        <v>0.5483</v>
+        <v>0.0639</v>
       </c>
       <c r="F563" s="7" t="n">
-        <v>59.38</v>
+        <v>55.61</v>
       </c>
       <c r="G563" s="6" t="inlineStr"/>
       <c r="H563" s="7" t="n">
-        <v>19.98</v>
+        <v>19.82</v>
       </c>
       <c r="I563" s="8" t="n">
-        <v>-0.1124</v>
+        <v>-0.3366</v>
       </c>
       <c r="J563" s="8" t="n">
-        <v>-1.529</v>
+        <v>0.5811999999999999</v>
       </c>
       <c r="K563" s="6" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L563" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST KATILIM TÜM</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M563" s="6" t="inlineStr"/>
@@ -24922,44 +24920,42 @@
     <row r="564">
       <c r="A564" s="2" t="inlineStr">
         <is>
-          <t>KTLEV</t>
+          <t>COSMO</t>
         </is>
       </c>
       <c r="B564" s="3" t="n">
-        <v>121.3</v>
+        <v>219.9</v>
       </c>
       <c r="C564" s="4" t="n">
-        <v>0.0185</v>
+        <v>0.08380000000000001</v>
       </c>
       <c r="D564" s="5" t="n">
-        <v>31940000</v>
+        <v>76070</v>
       </c>
       <c r="E564" s="4" t="n">
-        <v>0.2784</v>
+        <v>0.5483</v>
       </c>
       <c r="F564" s="3" t="n">
-        <v>92.09</v>
-      </c>
-      <c r="G564" s="3" t="n">
-        <v>29.13</v>
-      </c>
+        <v>59.38</v>
+      </c>
+      <c r="G564" s="2" t="inlineStr"/>
       <c r="H564" s="3" t="n">
-        <v>22.06</v>
+        <v>19.98</v>
       </c>
       <c r="I564" s="4" t="n">
-        <v>1.1992</v>
+        <v>-0.1124</v>
       </c>
       <c r="J564" s="4" t="n">
-        <v>0.3524</v>
+        <v>-1.529</v>
       </c>
       <c r="K564" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="L564" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST MALİ, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU, BIST KATILIM 50, BIST KATILIM 30, BIST KATILIM TEMETTU, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST KATILIM TÜM</t>
         </is>
       </c>
       <c r="M564" s="2" t="inlineStr"/>
@@ -24967,44 +24963,40 @@
     <row r="565">
       <c r="A565" s="6" t="inlineStr">
         <is>
-          <t>PASEU</t>
+          <t>KUYAS</t>
         </is>
       </c>
       <c r="B565" s="7" t="n">
-        <v>121</v>
+        <v>91.05</v>
       </c>
       <c r="C565" s="8" t="n">
-        <v>0.0689</v>
+        <v>0.0173</v>
       </c>
       <c r="D565" s="9" t="n">
-        <v>62680000</v>
+        <v>9490000</v>
       </c>
       <c r="E565" s="8" t="n">
-        <v>0.3205</v>
+        <v>0.9983</v>
       </c>
       <c r="F565" s="7" t="n">
-        <v>49.79</v>
-      </c>
-      <c r="G565" s="7" t="n">
-        <v>74.54000000000001</v>
-      </c>
+        <v>62.91</v>
+      </c>
+      <c r="G565" s="6" t="inlineStr"/>
       <c r="H565" s="7" t="n">
-        <v>23.17</v>
+        <v>20.55</v>
       </c>
       <c r="I565" s="8" t="n">
-        <v>0.4103</v>
-      </c>
-      <c r="J565" s="8" t="n">
-        <v>30.5521</v>
-      </c>
+        <v>-0.6668000000000001</v>
+      </c>
+      <c r="J565" s="6" t="inlineStr"/>
       <c r="K565" s="6" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L565" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST ULASTIRMA, BIST TÜM, BIST 50, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST 50-30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10, STOXX Emerging Markets 1500</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST İNŞAAT, BIST HİZMETLER, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST 50-30, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
         </is>
       </c>
       <c r="M565" s="6" t="inlineStr"/>
@@ -25012,44 +25004,44 @@
     <row r="566">
       <c r="A566" s="2" t="inlineStr">
         <is>
-          <t>UFUK</t>
-        </is>
-      </c>
-      <c r="B566" s="5" t="n">
-        <v>1390</v>
+          <t>PASEU</t>
+        </is>
+      </c>
+      <c r="B566" s="3" t="n">
+        <v>121</v>
       </c>
       <c r="C566" s="4" t="n">
-        <v>-0.0204</v>
+        <v>0.0689</v>
       </c>
       <c r="D566" s="5" t="n">
-        <v>31450</v>
+        <v>62680000</v>
       </c>
       <c r="E566" s="4" t="n">
-        <v>0.3704</v>
+        <v>0.3205</v>
       </c>
       <c r="F566" s="3" t="n">
-        <v>33.73</v>
+        <v>49.79</v>
       </c>
       <c r="G566" s="3" t="n">
-        <v>133.62</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="H566" s="3" t="n">
-        <v>24.23</v>
+        <v>23.17</v>
       </c>
       <c r="I566" s="4" t="n">
-        <v>0.2266</v>
+        <v>0.4103</v>
       </c>
       <c r="J566" s="4" t="n">
-        <v>-1.0967</v>
+        <v>30.5521</v>
       </c>
       <c r="K566" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Taşımacılık</t>
         </is>
       </c>
       <c r="L566" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST ULASTIRMA, BIST TÜM, BIST 50, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST 50-30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10, STOXX Emerging Markets 1500</t>
         </is>
       </c>
       <c r="M566" s="2" t="inlineStr"/>
@@ -25057,42 +25049,44 @@
     <row r="567">
       <c r="A567" s="6" t="inlineStr">
         <is>
-          <t>IEYHO</t>
-        </is>
-      </c>
-      <c r="B567" s="7" t="n">
-        <v>103</v>
+          <t>UFUK</t>
+        </is>
+      </c>
+      <c r="B567" s="9" t="n">
+        <v>1390</v>
       </c>
       <c r="C567" s="8" t="n">
-        <v>0.0148</v>
+        <v>-0.0204</v>
       </c>
       <c r="D567" s="9" t="n">
-        <v>4740000</v>
+        <v>31450</v>
       </c>
       <c r="E567" s="8" t="n">
-        <v>0.3576</v>
+        <v>0.3704</v>
       </c>
       <c r="F567" s="7" t="n">
-        <v>85.84</v>
-      </c>
-      <c r="G567" s="6" t="inlineStr"/>
+        <v>33.73</v>
+      </c>
+      <c r="G567" s="7" t="n">
+        <v>133.62</v>
+      </c>
       <c r="H567" s="7" t="n">
-        <v>24.67</v>
+        <v>24.23</v>
       </c>
       <c r="I567" s="8" t="n">
-        <v>-0.2916</v>
+        <v>0.2266</v>
       </c>
       <c r="J567" s="8" t="n">
-        <v>-0.6609</v>
+        <v>-1.0967</v>
       </c>
       <c r="K567" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L567" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST YILDIZ, STOXX Emerging Markets 1500</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M567" s="6" t="inlineStr"/>
@@ -25100,42 +25094,42 @@
     <row r="568">
       <c r="A568" s="2" t="inlineStr">
         <is>
-          <t>KUYAS</t>
+          <t>IEYHO</t>
         </is>
       </c>
       <c r="B568" s="3" t="n">
-        <v>91.05</v>
+        <v>103</v>
       </c>
       <c r="C568" s="4" t="n">
-        <v>0.0173</v>
+        <v>0.0148</v>
       </c>
       <c r="D568" s="5" t="n">
-        <v>9490000</v>
+        <v>4740000</v>
       </c>
       <c r="E568" s="4" t="n">
-        <v>0.9983</v>
+        <v>0.3576</v>
       </c>
       <c r="F568" s="3" t="n">
-        <v>62.91</v>
+        <v>85.84</v>
       </c>
       <c r="G568" s="2" t="inlineStr"/>
       <c r="H568" s="3" t="n">
-        <v>25.39</v>
+        <v>24.67</v>
       </c>
       <c r="I568" s="4" t="n">
-        <v>-0.7977</v>
+        <v>-0.2916</v>
       </c>
       <c r="J568" s="4" t="n">
-        <v>-4.018899999999999</v>
+        <v>-0.6609</v>
       </c>
       <c r="K568" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L568" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST İNŞAAT, BIST HİZMETLER, BIST İSTANBUL, BIST 100-30, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST 50-30, BIST 50-30 AGIRLIK SINIRLAMALI 25, BIST 50-30 AĞIRLIK SINIRLAMALI 10</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST İSTANBUL, BIST YILDIZ, STOXX Emerging Markets 1500</t>
         </is>
       </c>
       <c r="M568" s="2" t="inlineStr"/>
@@ -25829,21 +25823,21 @@
     <row r="585">
       <c r="A585" s="6" t="inlineStr">
         <is>
-          <t>EMPAE</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="B585" s="7" t="n">
-        <v>58.2</v>
+        <v>17.89</v>
       </c>
       <c r="C585" s="8" t="n">
-        <v>0.0992</v>
+        <v>-0.0438</v>
       </c>
       <c r="D585" s="9" t="n">
-        <v>21250000</v>
+        <v>66660000</v>
       </c>
       <c r="E585" s="6" t="inlineStr"/>
       <c r="F585" s="7" t="n">
-        <v>79.48</v>
+        <v>54.49</v>
       </c>
       <c r="G585" s="6" t="inlineStr"/>
       <c r="H585" s="6" t="inlineStr"/>
@@ -25851,12 +25845,12 @@
       <c r="J585" s="6" t="inlineStr"/>
       <c r="K585" s="6" t="inlineStr">
         <is>
-          <t>Elektronik teknoloji</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L585" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M585" s="6" t="inlineStr"/>
@@ -25864,89 +25858,97 @@
     <row r="586">
       <c r="A586" s="2" t="inlineStr">
         <is>
-          <t>BRMEN</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="B586" s="3" t="n">
-        <v>9.6</v>
+        <v>14.47</v>
       </c>
       <c r="C586" s="4" t="n">
-        <v>-0.0194</v>
-      </c>
-      <c r="D586" s="5" t="n">
-        <v>961350</v>
-      </c>
-      <c r="E586" s="4" t="n">
-        <v>0.95</v>
-      </c>
+        <v>-0.0366</v>
+      </c>
+      <c r="D586" s="3" t="n">
+        <v>32410000</v>
+      </c>
+      <c r="E586" s="2" t="inlineStr"/>
       <c r="F586" s="3" t="n">
-        <v>60.81</v>
+        <v>55.48</v>
       </c>
       <c r="G586" s="2" t="inlineStr"/>
       <c r="H586" s="2" t="inlineStr"/>
-      <c r="I586" s="4" t="n">
-        <v>-23.6291</v>
-      </c>
-      <c r="J586" s="4" t="n">
-        <v>-0.4678</v>
-      </c>
+      <c r="I586" s="2" t="inlineStr"/>
+      <c r="J586" s="2" t="inlineStr"/>
       <c r="K586" s="2" t="inlineStr">
         <is>
           <t>İşlenebilen endüstriler</t>
         </is>
       </c>
-      <c r="L586" s="2" t="inlineStr"/>
+      <c r="L586" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
+        </is>
+      </c>
       <c r="M586" s="2" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" s="6" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>ARZUM</t>
         </is>
       </c>
       <c r="B587" s="7" t="n">
-        <v>79.3</v>
+        <v>2.63</v>
       </c>
       <c r="C587" s="8" t="n">
-        <v>-0.021</v>
+        <v>-0.0295</v>
       </c>
       <c r="D587" s="9" t="n">
-        <v>171630</v>
-      </c>
-      <c r="E587" s="6" t="inlineStr"/>
+        <v>28760000</v>
+      </c>
+      <c r="E587" s="8" t="n">
+        <v>0.7119</v>
+      </c>
       <c r="F587" s="7" t="n">
-        <v>11.3</v>
+        <v>41.18</v>
       </c>
       <c r="G587" s="6" t="inlineStr"/>
       <c r="H587" s="6" t="inlineStr"/>
-      <c r="I587" s="6" t="inlineStr"/>
-      <c r="J587" s="6" t="inlineStr"/>
+      <c r="I587" s="8" t="n">
+        <v>-191.6342</v>
+      </c>
+      <c r="J587" s="8" t="n">
+        <v>-0.8093</v>
+      </c>
       <c r="K587" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L587" s="6" t="inlineStr"/>
+          <t>Dağıtım servisleri</t>
+        </is>
+      </c>
+      <c r="L587" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
+        </is>
+      </c>
       <c r="M587" s="6" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="B588" s="3" t="n">
-        <v>14.47</v>
+        <v>30.7</v>
       </c>
       <c r="C588" s="4" t="n">
-        <v>-0.0366</v>
-      </c>
-      <c r="D588" s="3" t="n">
-        <v>32410000</v>
+        <v>-0.0007000000000000001</v>
+      </c>
+      <c r="D588" s="5" t="n">
+        <v>26120000</v>
       </c>
       <c r="E588" s="2" t="inlineStr"/>
       <c r="F588" s="3" t="n">
-        <v>55.48</v>
+        <v>68.69</v>
       </c>
       <c r="G588" s="2" t="inlineStr"/>
       <c r="H588" s="2" t="inlineStr"/>
@@ -25954,12 +25956,12 @@
       <c r="J588" s="2" t="inlineStr"/>
       <c r="K588" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="L588" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
+          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M588" s="2" t="inlineStr"/>
@@ -25967,23 +25969,21 @@
     <row r="589">
       <c r="A589" s="6" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="B589" s="7" t="n">
-        <v>31.36</v>
+        <v>79.3</v>
       </c>
       <c r="C589" s="8" t="n">
-        <v>0.0058</v>
+        <v>-0.021</v>
       </c>
       <c r="D589" s="9" t="n">
-        <v>14110000</v>
-      </c>
-      <c r="E589" s="8" t="n">
-        <v>0.2667</v>
-      </c>
+        <v>171630</v>
+      </c>
+      <c r="E589" s="6" t="inlineStr"/>
       <c r="F589" s="7" t="n">
-        <v>60.8</v>
+        <v>11.3</v>
       </c>
       <c r="G589" s="6" t="inlineStr"/>
       <c r="H589" s="6" t="inlineStr"/>
@@ -25991,39 +25991,41 @@
       <c r="J589" s="6" t="inlineStr"/>
       <c r="K589" s="6" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
-        </is>
-      </c>
-      <c r="L589" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
-        </is>
-      </c>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L589" s="6" t="inlineStr"/>
       <c r="M589" s="6" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" s="2" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>BORLS</t>
         </is>
       </c>
       <c r="B590" s="3" t="n">
-        <v>17.89</v>
+        <v>6.34</v>
       </c>
       <c r="C590" s="4" t="n">
-        <v>-0.0438</v>
+        <v>-0.0745</v>
       </c>
       <c r="D590" s="5" t="n">
-        <v>66660000</v>
-      </c>
-      <c r="E590" s="2" t="inlineStr"/>
+        <v>57090000</v>
+      </c>
+      <c r="E590" s="4" t="n">
+        <v>0.1672</v>
+      </c>
       <c r="F590" s="3" t="n">
-        <v>54.49</v>
+        <v>51.71</v>
       </c>
       <c r="G590" s="2" t="inlineStr"/>
       <c r="H590" s="2" t="inlineStr"/>
-      <c r="I590" s="2" t="inlineStr"/>
-      <c r="J590" s="2" t="inlineStr"/>
+      <c r="I590" s="4" t="n">
+        <v>-5.3262</v>
+      </c>
+      <c r="J590" s="4" t="n">
+        <v>-4.2562</v>
+      </c>
       <c r="K590" s="2" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -26031,7 +26033,7 @@
       </c>
       <c r="L590" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M590" s="2" t="inlineStr"/>
@@ -26039,40 +26041,36 @@
     <row r="591">
       <c r="A591" s="6" t="inlineStr">
         <is>
-          <t>GRNYO</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="B591" s="7" t="n">
-        <v>19.78</v>
+        <v>31.36</v>
       </c>
       <c r="C591" s="8" t="n">
-        <v>-0.0639</v>
+        <v>0.0058</v>
       </c>
       <c r="D591" s="9" t="n">
-        <v>711640</v>
+        <v>14110000</v>
       </c>
       <c r="E591" s="8" t="n">
-        <v>0.9869</v>
+        <v>0.2667</v>
       </c>
       <c r="F591" s="7" t="n">
-        <v>60.87</v>
+        <v>60.8</v>
       </c>
       <c r="G591" s="6" t="inlineStr"/>
       <c r="H591" s="6" t="inlineStr"/>
-      <c r="I591" s="8" t="n">
-        <v>-0.2446</v>
-      </c>
-      <c r="J591" s="8" t="n">
-        <v>0.3246</v>
-      </c>
+      <c r="I591" s="6" t="inlineStr"/>
+      <c r="J591" s="6" t="inlineStr"/>
       <c r="K591" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="L591" s="6" t="inlineStr">
         <is>
-          <t>BIST MENKUL KIYM YO</t>
+          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M591" s="6" t="inlineStr"/>
@@ -26080,21 +26078,23 @@
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>ICUGS</t>
         </is>
       </c>
       <c r="B592" s="3" t="n">
-        <v>203.2</v>
+        <v>6.06</v>
       </c>
       <c r="C592" s="4" t="n">
-        <v>0.0114</v>
+        <v>-0.008199999999999999</v>
       </c>
       <c r="D592" s="5" t="n">
-        <v>7230000</v>
-      </c>
-      <c r="E592" s="2" t="inlineStr"/>
+        <v>44330000</v>
+      </c>
+      <c r="E592" s="4" t="n">
+        <v>0.8667</v>
+      </c>
       <c r="F592" s="3" t="n">
-        <v>71.43000000000001</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="G592" s="2" t="inlineStr"/>
       <c r="H592" s="2" t="inlineStr"/>
@@ -26102,12 +26102,12 @@
       <c r="J592" s="2" t="inlineStr"/>
       <c r="K592" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L592" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
         </is>
       </c>
       <c r="M592" s="2" t="inlineStr"/>
@@ -26115,21 +26115,21 @@
     <row r="593">
       <c r="A593" s="6" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>AAGYO</t>
         </is>
       </c>
       <c r="B593" s="7" t="n">
-        <v>30.7</v>
+        <v>18.92</v>
       </c>
       <c r="C593" s="8" t="n">
-        <v>-0.0007000000000000001</v>
+        <v>-0.0257</v>
       </c>
       <c r="D593" s="9" t="n">
-        <v>26120000</v>
+        <v>61340000</v>
       </c>
       <c r="E593" s="6" t="inlineStr"/>
       <c r="F593" s="7" t="n">
-        <v>68.69</v>
+        <v>36.26</v>
       </c>
       <c r="G593" s="6" t="inlineStr"/>
       <c r="H593" s="6" t="inlineStr"/>
@@ -26137,12 +26137,12 @@
       <c r="J593" s="6" t="inlineStr"/>
       <c r="K593" s="6" t="inlineStr">
         <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L593" s="6" t="inlineStr">
         <is>
-          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
         </is>
       </c>
       <c r="M593" s="6" t="inlineStr"/>
@@ -26150,21 +26150,21 @@
     <row r="594">
       <c r="A594" s="2" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>EMPAE</t>
         </is>
       </c>
       <c r="B594" s="3" t="n">
-        <v>6.12</v>
+        <v>58.2</v>
       </c>
       <c r="C594" s="4" t="n">
-        <v>-0.006500000000000001</v>
+        <v>0.0992</v>
       </c>
       <c r="D594" s="5" t="n">
-        <v>7340000</v>
+        <v>21250000</v>
       </c>
       <c r="E594" s="2" t="inlineStr"/>
       <c r="F594" s="3" t="n">
-        <v>53.81</v>
+        <v>79.48</v>
       </c>
       <c r="G594" s="2" t="inlineStr"/>
       <c r="H594" s="2" t="inlineStr"/>
@@ -26172,51 +26172,47 @@
       <c r="J594" s="2" t="inlineStr"/>
       <c r="K594" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L594" s="2" t="inlineStr"/>
+          <t>Elektronik teknoloji</t>
+        </is>
+      </c>
+      <c r="L594" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
+        </is>
+      </c>
       <c r="M594" s="2" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" s="6" t="inlineStr">
         <is>
-          <t>BERA</t>
+          <t>CGCAM</t>
         </is>
       </c>
       <c r="B595" s="7" t="n">
-        <v>17.39</v>
+        <v>45.46</v>
       </c>
       <c r="C595" s="8" t="n">
-        <v>-0.023</v>
+        <v>0.0102</v>
       </c>
       <c r="D595" s="9" t="n">
-        <v>16640000</v>
-      </c>
-      <c r="E595" s="8" t="n">
-        <v>0.9246</v>
-      </c>
+        <v>6120000</v>
+      </c>
+      <c r="E595" s="6" t="inlineStr"/>
       <c r="F595" s="7" t="n">
-        <v>49.27</v>
-      </c>
-      <c r="G595" s="7" t="n">
-        <v>164.37</v>
-      </c>
+        <v>67.47</v>
+      </c>
+      <c r="G595" s="6" t="inlineStr"/>
       <c r="H595" s="6" t="inlineStr"/>
-      <c r="I595" s="8" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="J595" s="8" t="n">
-        <v>-10.3171</v>
-      </c>
+      <c r="I595" s="6" t="inlineStr"/>
+      <c r="J595" s="6" t="inlineStr"/>
       <c r="K595" s="6" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="L595" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
         </is>
       </c>
       <c r="M595" s="6" t="inlineStr"/>
@@ -26224,40 +26220,34 @@
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
         <is>
-          <t>ARZUM</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="B596" s="3" t="n">
-        <v>2.63</v>
+        <v>35.76</v>
       </c>
       <c r="C596" s="4" t="n">
-        <v>-0.0295</v>
+        <v>-0.0245</v>
       </c>
       <c r="D596" s="5" t="n">
-        <v>28760000</v>
-      </c>
-      <c r="E596" s="4" t="n">
-        <v>0.7119</v>
-      </c>
+        <v>5260000</v>
+      </c>
+      <c r="E596" s="2" t="inlineStr"/>
       <c r="F596" s="3" t="n">
-        <v>41.18</v>
+        <v>59.16</v>
       </c>
       <c r="G596" s="2" t="inlineStr"/>
       <c r="H596" s="2" t="inlineStr"/>
-      <c r="I596" s="4" t="n">
-        <v>-191.6342</v>
-      </c>
-      <c r="J596" s="4" t="n">
-        <v>-0.8093</v>
-      </c>
+      <c r="I596" s="2" t="inlineStr"/>
+      <c r="J596" s="2" t="inlineStr"/>
       <c r="K596" s="2" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L596" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
         </is>
       </c>
       <c r="M596" s="2" t="inlineStr"/>
@@ -26265,100 +26255,102 @@
     <row r="597">
       <c r="A597" s="6" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>INTEK</t>
         </is>
       </c>
       <c r="B597" s="7" t="n">
-        <v>80.04000000000001</v>
+        <v>244.25</v>
       </c>
       <c r="C597" s="8" t="n">
-        <v>-0.009399999999999999</v>
+        <v>-0.0338</v>
       </c>
       <c r="D597" s="9" t="n">
-        <v>10710000</v>
-      </c>
-      <c r="E597" s="6" t="inlineStr"/>
+        <v>10010</v>
+      </c>
+      <c r="E597" s="8" t="n">
+        <v>0.2578</v>
+      </c>
       <c r="F597" s="7" t="n">
-        <v>43.25</v>
+        <v>45.91</v>
       </c>
       <c r="G597" s="6" t="inlineStr"/>
       <c r="H597" s="6" t="inlineStr"/>
       <c r="I597" s="6" t="inlineStr"/>
       <c r="J597" s="6" t="inlineStr"/>
-      <c r="K597" s="6" t="inlineStr"/>
+      <c r="K597" s="6" t="inlineStr">
+        <is>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
       <c r="L597" s="6" t="inlineStr"/>
       <c r="M597" s="6" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
         <is>
-          <t>NETAS</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="B598" s="3" t="n">
-        <v>70.15000000000001</v>
+        <v>6.12</v>
       </c>
       <c r="C598" s="4" t="n">
-        <v>-0.0134</v>
+        <v>-0.006500000000000001</v>
       </c>
       <c r="D598" s="5" t="n">
-        <v>862740</v>
-      </c>
-      <c r="E598" s="4" t="n">
-        <v>0.3695000000000001</v>
-      </c>
+        <v>7340000</v>
+      </c>
+      <c r="E598" s="2" t="inlineStr"/>
       <c r="F598" s="3" t="n">
-        <v>64.09</v>
+        <v>53.81</v>
       </c>
       <c r="G598" s="2" t="inlineStr"/>
       <c r="H598" s="2" t="inlineStr"/>
       <c r="I598" s="2" t="inlineStr"/>
-      <c r="J598" s="4" t="n">
-        <v>0.1431</v>
-      </c>
+      <c r="J598" s="2" t="inlineStr"/>
       <c r="K598" s="2" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
-        </is>
-      </c>
-      <c r="L598" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
-        </is>
-      </c>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L598" s="2" t="inlineStr"/>
       <c r="M598" s="2" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" s="6" t="inlineStr">
         <is>
-          <t>CGCAM</t>
+          <t>NETAS</t>
         </is>
       </c>
       <c r="B599" s="7" t="n">
-        <v>45.46</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="C599" s="8" t="n">
-        <v>0.0102</v>
+        <v>-0.0134</v>
       </c>
       <c r="D599" s="9" t="n">
-        <v>6120000</v>
-      </c>
-      <c r="E599" s="6" t="inlineStr"/>
+        <v>862740</v>
+      </c>
+      <c r="E599" s="8" t="n">
+        <v>0.3695000000000001</v>
+      </c>
       <c r="F599" s="7" t="n">
-        <v>67.47</v>
+        <v>64.09</v>
       </c>
       <c r="G599" s="6" t="inlineStr"/>
       <c r="H599" s="6" t="inlineStr"/>
       <c r="I599" s="6" t="inlineStr"/>
-      <c r="J599" s="6" t="inlineStr"/>
+      <c r="J599" s="8" t="n">
+        <v>0.1431</v>
+      </c>
       <c r="K599" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="L599" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M599" s="6" t="inlineStr"/>
@@ -26366,42 +26358,42 @@
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B600" s="3" t="n">
-        <v>35.16</v>
+        <v>115</v>
       </c>
       <c r="C600" s="4" t="n">
-        <v>-0.0228</v>
+        <v>-0.0566</v>
       </c>
       <c r="D600" s="5" t="n">
-        <v>5700000</v>
+        <v>21130000</v>
       </c>
       <c r="E600" s="4" t="n">
-        <v>0.3528</v>
+        <v>0.4894</v>
       </c>
       <c r="F600" s="3" t="n">
-        <v>42.83</v>
+        <v>50.2</v>
       </c>
       <c r="G600" s="3" t="n">
-        <v>13.9</v>
+        <v>13.6</v>
       </c>
       <c r="H600" s="2" t="inlineStr"/>
       <c r="I600" s="4" t="n">
-        <v>0.1029</v>
+        <v>0.0735</v>
       </c>
       <c r="J600" s="4" t="n">
-        <v>-1.4864</v>
+        <v>0.1091</v>
       </c>
       <c r="K600" s="2" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>İletişim</t>
         </is>
       </c>
       <c r="L600" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST ORMAN KAĞIT BASIM, BIST YILDIZ, BIST TEMETTU, BIST KURUMSAL YÖNETİM, BIST TEKİRDAĞ</t>
+          <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST İLETİŞİM, BIST HİZMETLER, BIST İSTANBUL, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500, STOXX Eastern Europe 50</t>
         </is>
       </c>
       <c r="M600" s="2" t="inlineStr"/>
@@ -26409,26 +26401,34 @@
     <row r="601">
       <c r="A601" s="6" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>BERA</t>
         </is>
       </c>
       <c r="B601" s="7" t="n">
-        <v>35.76</v>
+        <v>17.39</v>
       </c>
       <c r="C601" s="8" t="n">
-        <v>-0.0245</v>
+        <v>-0.023</v>
       </c>
       <c r="D601" s="9" t="n">
-        <v>5260000</v>
-      </c>
-      <c r="E601" s="6" t="inlineStr"/>
+        <v>16640000</v>
+      </c>
+      <c r="E601" s="8" t="n">
+        <v>0.9246</v>
+      </c>
       <c r="F601" s="7" t="n">
-        <v>59.16</v>
-      </c>
-      <c r="G601" s="6" t="inlineStr"/>
+        <v>49.27</v>
+      </c>
+      <c r="G601" s="7" t="n">
+        <v>164.37</v>
+      </c>
       <c r="H601" s="6" t="inlineStr"/>
-      <c r="I601" s="6" t="inlineStr"/>
-      <c r="J601" s="6" t="inlineStr"/>
+      <c r="I601" s="8" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="J601" s="8" t="n">
+        <v>-10.3171</v>
+      </c>
       <c r="K601" s="6" t="inlineStr">
         <is>
           <t>Üretici imalatı</t>
@@ -26436,7 +26436,7 @@
       </c>
       <c r="L601" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
         </is>
       </c>
       <c r="M601" s="6" t="inlineStr"/>
@@ -26444,23 +26444,21 @@
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
         <is>
-          <t>INTEK</t>
+          <t>SMRVA</t>
         </is>
       </c>
       <c r="B602" s="3" t="n">
-        <v>244.25</v>
+        <v>18.01</v>
       </c>
       <c r="C602" s="4" t="n">
-        <v>-0.0338</v>
+        <v>-0.0317</v>
       </c>
       <c r="D602" s="5" t="n">
-        <v>10010</v>
-      </c>
-      <c r="E602" s="4" t="n">
-        <v>0.2578</v>
-      </c>
+        <v>61370000</v>
+      </c>
+      <c r="E602" s="2" t="inlineStr"/>
       <c r="F602" s="3" t="n">
-        <v>45.91</v>
+        <v>52.71</v>
       </c>
       <c r="G602" s="2" t="inlineStr"/>
       <c r="H602" s="2" t="inlineStr"/>
@@ -26468,51 +26466,47 @@
       <c r="J602" s="2" t="inlineStr"/>
       <c r="K602" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L602" s="2" t="inlineStr"/>
+          <t>Ticari hizmetler</t>
+        </is>
+      </c>
+      <c r="L602" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
+        </is>
+      </c>
       <c r="M602" s="2" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" s="6" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="B603" s="7" t="n">
-        <v>115</v>
+        <v>203.2</v>
       </c>
       <c r="C603" s="8" t="n">
-        <v>-0.0566</v>
+        <v>0.0114</v>
       </c>
       <c r="D603" s="9" t="n">
-        <v>21130000</v>
-      </c>
-      <c r="E603" s="8" t="n">
-        <v>0.4894</v>
-      </c>
+        <v>7230000</v>
+      </c>
+      <c r="E603" s="6" t="inlineStr"/>
       <c r="F603" s="7" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="G603" s="7" t="n">
-        <v>13.6</v>
-      </c>
+        <v>71.43000000000001</v>
+      </c>
+      <c r="G603" s="6" t="inlineStr"/>
       <c r="H603" s="6" t="inlineStr"/>
-      <c r="I603" s="8" t="n">
-        <v>0.0735</v>
-      </c>
-      <c r="J603" s="8" t="n">
-        <v>0.1091</v>
-      </c>
+      <c r="I603" s="6" t="inlineStr"/>
+      <c r="J603" s="6" t="inlineStr"/>
       <c r="K603" s="6" t="inlineStr">
         <is>
-          <t>İletişim</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="L603" s="6" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST İLETİŞİM, BIST HİZMETLER, BIST İSTANBUL, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500, STOXX Eastern Europe 50</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
         </is>
       </c>
       <c r="M603" s="6" t="inlineStr"/>
@@ -26520,40 +26514,34 @@
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
         <is>
-          <t>CRFSA</t>
+          <t>GLRMK</t>
         </is>
       </c>
       <c r="B604" s="3" t="n">
-        <v>148.6</v>
+        <v>205</v>
       </c>
       <c r="C604" s="4" t="n">
-        <v>-0.0237</v>
+        <v>0.0029</v>
       </c>
       <c r="D604" s="5" t="n">
-        <v>1120000</v>
-      </c>
-      <c r="E604" s="4" t="n">
-        <v>0.1071</v>
-      </c>
+        <v>11560000</v>
+      </c>
+      <c r="E604" s="2" t="inlineStr"/>
       <c r="F604" s="3" t="n">
-        <v>51.67</v>
+        <v>53.72</v>
       </c>
       <c r="G604" s="2" t="inlineStr"/>
       <c r="H604" s="2" t="inlineStr"/>
-      <c r="I604" s="4" t="n">
-        <v>-3.6635</v>
-      </c>
-      <c r="J604" s="4" t="n">
-        <v>-0.4897</v>
-      </c>
+      <c r="I604" s="2" t="inlineStr"/>
+      <c r="J604" s="2" t="inlineStr"/>
       <c r="K604" s="2" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="L604" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
         </is>
       </c>
       <c r="M604" s="2" t="inlineStr"/>
@@ -26561,34 +26549,42 @@
     <row r="605">
       <c r="A605" s="6" t="inlineStr">
         <is>
-          <t>AAGYO</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="B605" s="7" t="n">
-        <v>18.92</v>
+        <v>35.16</v>
       </c>
       <c r="C605" s="8" t="n">
-        <v>-0.0257</v>
+        <v>-0.0228</v>
       </c>
       <c r="D605" s="9" t="n">
-        <v>61340000</v>
-      </c>
-      <c r="E605" s="6" t="inlineStr"/>
+        <v>5700000</v>
+      </c>
+      <c r="E605" s="8" t="n">
+        <v>0.3528</v>
+      </c>
       <c r="F605" s="7" t="n">
-        <v>36.26</v>
-      </c>
-      <c r="G605" s="6" t="inlineStr"/>
+        <v>42.83</v>
+      </c>
+      <c r="G605" s="7" t="n">
+        <v>13.9</v>
+      </c>
       <c r="H605" s="6" t="inlineStr"/>
-      <c r="I605" s="6" t="inlineStr"/>
-      <c r="J605" s="6" t="inlineStr"/>
+      <c r="I605" s="8" t="n">
+        <v>0.1029</v>
+      </c>
+      <c r="J605" s="8" t="n">
+        <v>-1.4864</v>
+      </c>
       <c r="K605" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
         </is>
       </c>
       <c r="L605" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST ORMAN KAĞIT BASIM, BIST YILDIZ, BIST TEMETTU, BIST KURUMSAL YÖNETİM, BIST TEKİRDAĞ</t>
         </is>
       </c>
       <c r="M605" s="6" t="inlineStr"/>
@@ -26596,34 +26592,40 @@
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
         <is>
-          <t>GLRMK</t>
+          <t>CRFSA</t>
         </is>
       </c>
       <c r="B606" s="3" t="n">
-        <v>205</v>
+        <v>148.6</v>
       </c>
       <c r="C606" s="4" t="n">
-        <v>0.0029</v>
+        <v>-0.0237</v>
       </c>
       <c r="D606" s="5" t="n">
-        <v>11560000</v>
-      </c>
-      <c r="E606" s="2" t="inlineStr"/>
+        <v>1120000</v>
+      </c>
+      <c r="E606" s="4" t="n">
+        <v>0.1071</v>
+      </c>
       <c r="F606" s="3" t="n">
-        <v>53.72</v>
+        <v>51.67</v>
       </c>
       <c r="G606" s="2" t="inlineStr"/>
       <c r="H606" s="2" t="inlineStr"/>
-      <c r="I606" s="2" t="inlineStr"/>
-      <c r="J606" s="2" t="inlineStr"/>
+      <c r="I606" s="4" t="n">
+        <v>-3.6635</v>
+      </c>
+      <c r="J606" s="4" t="n">
+        <v>-0.4897</v>
+      </c>
       <c r="K606" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="L606" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
         </is>
       </c>
       <c r="M606" s="2" t="inlineStr"/>
@@ -26631,65 +26633,59 @@
     <row r="607">
       <c r="A607" s="6" t="inlineStr">
         <is>
-          <t>MMCAS</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="B607" s="7" t="n">
-        <v>76.8</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="C607" s="8" t="n">
-        <v>-0.0235</v>
+        <v>-0.009399999999999999</v>
       </c>
       <c r="D607" s="9" t="n">
-        <v>60180</v>
-      </c>
-      <c r="E607" s="8" t="n">
-        <v>0.58</v>
-      </c>
+        <v>10710000</v>
+      </c>
+      <c r="E607" s="6" t="inlineStr"/>
       <c r="F607" s="7" t="n">
-        <v>43.15</v>
+        <v>43.25</v>
       </c>
       <c r="G607" s="6" t="inlineStr"/>
       <c r="H607" s="6" t="inlineStr"/>
-      <c r="I607" s="8" t="n">
-        <v>-9.409700000000001</v>
-      </c>
-      <c r="J607" s="8" t="n">
-        <v>-4.155</v>
-      </c>
-      <c r="K607" s="6" t="inlineStr">
-        <is>
-          <t>Taşımacılık</t>
-        </is>
-      </c>
+      <c r="I607" s="6" t="inlineStr"/>
+      <c r="J607" s="6" t="inlineStr"/>
+      <c r="K607" s="6" t="inlineStr"/>
       <c r="L607" s="6" t="inlineStr"/>
       <c r="M607" s="6" t="inlineStr"/>
     </row>
     <row r="608">
       <c r="A608" s="2" t="inlineStr">
         <is>
-          <t>ICUGS</t>
+          <t>GRNYO</t>
         </is>
       </c>
       <c r="B608" s="3" t="n">
-        <v>6.06</v>
+        <v>19.78</v>
       </c>
       <c r="C608" s="4" t="n">
-        <v>-0.008199999999999999</v>
+        <v>-0.0639</v>
       </c>
       <c r="D608" s="5" t="n">
-        <v>44330000</v>
+        <v>711640</v>
       </c>
       <c r="E608" s="4" t="n">
-        <v>0.8667</v>
+        <v>0.9869</v>
       </c>
       <c r="F608" s="3" t="n">
-        <v>67.06999999999999</v>
+        <v>60.87</v>
       </c>
       <c r="G608" s="2" t="inlineStr"/>
       <c r="H608" s="2" t="inlineStr"/>
-      <c r="I608" s="2" t="inlineStr"/>
-      <c r="J608" s="2" t="inlineStr"/>
+      <c r="I608" s="4" t="n">
+        <v>-0.2446</v>
+      </c>
+      <c r="J608" s="4" t="n">
+        <v>0.3246</v>
+      </c>
       <c r="K608" s="2" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -26697,7 +26693,7 @@
       </c>
       <c r="L608" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
+          <t>BIST MENKUL KIYM YO</t>
         </is>
       </c>
       <c r="M608" s="2" t="inlineStr"/>
@@ -26705,32 +26701,26 @@
     <row r="609">
       <c r="A609" s="6" t="inlineStr">
         <is>
-          <t>BORLS</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="B609" s="7" t="n">
-        <v>6.34</v>
+        <v>2.88</v>
       </c>
       <c r="C609" s="8" t="n">
-        <v>-0.0745</v>
+        <v>-0.0368</v>
       </c>
       <c r="D609" s="9" t="n">
-        <v>57090000</v>
-      </c>
-      <c r="E609" s="8" t="n">
-        <v>0.1672</v>
-      </c>
+        <v>190570000</v>
+      </c>
+      <c r="E609" s="6" t="inlineStr"/>
       <c r="F609" s="7" t="n">
-        <v>51.71</v>
+        <v>52.36</v>
       </c>
       <c r="G609" s="6" t="inlineStr"/>
       <c r="H609" s="6" t="inlineStr"/>
-      <c r="I609" s="8" t="n">
-        <v>-5.3262</v>
-      </c>
-      <c r="J609" s="8" t="n">
-        <v>-4.2562</v>
-      </c>
+      <c r="I609" s="6" t="inlineStr"/>
+      <c r="J609" s="6" t="inlineStr"/>
       <c r="K609" s="6" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -26738,7 +26728,7 @@
       </c>
       <c r="L609" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M609" s="6" t="inlineStr"/>
@@ -26746,71 +26736,75 @@
     <row r="610">
       <c r="A610" s="2" t="inlineStr">
         <is>
-          <t>SMRVA</t>
+          <t>MMCAS</t>
         </is>
       </c>
       <c r="B610" s="3" t="n">
-        <v>18.01</v>
+        <v>76.8</v>
       </c>
       <c r="C610" s="4" t="n">
-        <v>-0.0317</v>
+        <v>-0.0235</v>
       </c>
       <c r="D610" s="5" t="n">
-        <v>61370000</v>
-      </c>
-      <c r="E610" s="2" t="inlineStr"/>
+        <v>60180</v>
+      </c>
+      <c r="E610" s="4" t="n">
+        <v>0.58</v>
+      </c>
       <c r="F610" s="3" t="n">
-        <v>52.71</v>
+        <v>43.15</v>
       </c>
       <c r="G610" s="2" t="inlineStr"/>
       <c r="H610" s="2" t="inlineStr"/>
-      <c r="I610" s="2" t="inlineStr"/>
-      <c r="J610" s="2" t="inlineStr"/>
+      <c r="I610" s="4" t="n">
+        <v>-9.409700000000001</v>
+      </c>
+      <c r="J610" s="4" t="n">
+        <v>-4.155</v>
+      </c>
       <c r="K610" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
-        </is>
-      </c>
-      <c r="L610" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
-        </is>
-      </c>
+          <t>Taşımacılık</t>
+        </is>
+      </c>
+      <c r="L610" s="2" t="inlineStr"/>
       <c r="M610" s="2" t="inlineStr"/>
     </row>
     <row r="611">
       <c r="A611" s="6" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>BRMEN</t>
         </is>
       </c>
       <c r="B611" s="7" t="n">
-        <v>2.88</v>
+        <v>9.6</v>
       </c>
       <c r="C611" s="8" t="n">
-        <v>-0.0368</v>
+        <v>-0.0194</v>
       </c>
       <c r="D611" s="9" t="n">
-        <v>190570000</v>
-      </c>
-      <c r="E611" s="6" t="inlineStr"/>
+        <v>961350</v>
+      </c>
+      <c r="E611" s="8" t="n">
+        <v>0.95</v>
+      </c>
       <c r="F611" s="7" t="n">
-        <v>52.36</v>
+        <v>60.81</v>
       </c>
       <c r="G611" s="6" t="inlineStr"/>
       <c r="H611" s="6" t="inlineStr"/>
-      <c r="I611" s="6" t="inlineStr"/>
-      <c r="J611" s="6" t="inlineStr"/>
+      <c r="I611" s="8" t="n">
+        <v>-23.6291</v>
+      </c>
+      <c r="J611" s="8" t="n">
+        <v>-0.4678</v>
+      </c>
       <c r="K611" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L611" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L611" s="6" t="inlineStr"/>
       <c r="M611" s="6" t="inlineStr"/>
     </row>
   </sheetData>
@@ -26835,7 +26829,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>12.05.2026 15:30</t>
+          <t>12.05.2026 16:30</t>
         </is>
       </c>
     </row>

--- a/data/bist_screener_2026-05-12.xlsx
+++ b/data/bist_screener_2026-05-12.xlsx
@@ -25823,21 +25823,21 @@
     <row r="585">
       <c r="A585" s="6" t="inlineStr">
         <is>
-          <t>LXGYO</t>
+          <t>GENKM</t>
         </is>
       </c>
       <c r="B585" s="7" t="n">
-        <v>17.89</v>
+        <v>14.47</v>
       </c>
       <c r="C585" s="8" t="n">
-        <v>-0.0438</v>
-      </c>
-      <c r="D585" s="9" t="n">
-        <v>66660000</v>
+        <v>-0.0366</v>
+      </c>
+      <c r="D585" s="7" t="n">
+        <v>32410000</v>
       </c>
       <c r="E585" s="6" t="inlineStr"/>
       <c r="F585" s="7" t="n">
-        <v>54.49</v>
+        <v>55.48</v>
       </c>
       <c r="G585" s="6" t="inlineStr"/>
       <c r="H585" s="6" t="inlineStr"/>
@@ -25845,12 +25845,12 @@
       <c r="J585" s="6" t="inlineStr"/>
       <c r="K585" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>İşlenebilen endüstriler</t>
         </is>
       </c>
       <c r="L585" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
         </is>
       </c>
       <c r="M585" s="6" t="inlineStr"/>
@@ -25858,21 +25858,21 @@
     <row r="586">
       <c r="A586" s="2" t="inlineStr">
         <is>
-          <t>GENKM</t>
+          <t>ENPRA</t>
         </is>
       </c>
       <c r="B586" s="3" t="n">
-        <v>14.47</v>
+        <v>79.3</v>
       </c>
       <c r="C586" s="4" t="n">
-        <v>-0.0366</v>
-      </c>
-      <c r="D586" s="3" t="n">
-        <v>32410000</v>
+        <v>-0.021</v>
+      </c>
+      <c r="D586" s="5" t="n">
+        <v>171630</v>
       </c>
       <c r="E586" s="2" t="inlineStr"/>
       <c r="F586" s="3" t="n">
-        <v>55.48</v>
+        <v>11.3</v>
       </c>
       <c r="G586" s="2" t="inlineStr"/>
       <c r="H586" s="2" t="inlineStr"/>
@@ -25880,53 +25880,43 @@
       <c r="J586" s="2" t="inlineStr"/>
       <c r="K586" s="2" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L586" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST KOCAELI</t>
-        </is>
-      </c>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L586" s="2" t="inlineStr"/>
       <c r="M586" s="2" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" s="6" t="inlineStr">
         <is>
-          <t>ARZUM</t>
+          <t>CGCAM</t>
         </is>
       </c>
       <c r="B587" s="7" t="n">
-        <v>2.63</v>
+        <v>45.46</v>
       </c>
       <c r="C587" s="8" t="n">
-        <v>-0.0295</v>
+        <v>0.0102</v>
       </c>
       <c r="D587" s="9" t="n">
-        <v>28760000</v>
-      </c>
-      <c r="E587" s="8" t="n">
-        <v>0.7119</v>
-      </c>
+        <v>6120000</v>
+      </c>
+      <c r="E587" s="6" t="inlineStr"/>
       <c r="F587" s="7" t="n">
-        <v>41.18</v>
+        <v>67.47</v>
       </c>
       <c r="G587" s="6" t="inlineStr"/>
       <c r="H587" s="6" t="inlineStr"/>
-      <c r="I587" s="8" t="n">
-        <v>-191.6342</v>
-      </c>
-      <c r="J587" s="8" t="n">
-        <v>-0.8093</v>
-      </c>
+      <c r="I587" s="6" t="inlineStr"/>
+      <c r="J587" s="6" t="inlineStr"/>
       <c r="K587" s="6" t="inlineStr">
         <is>
-          <t>Dağıtım servisleri</t>
+          <t>Dayanıklı tüketim malları</t>
         </is>
       </c>
       <c r="L587" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
         </is>
       </c>
       <c r="M587" s="6" t="inlineStr"/>
@@ -25934,56 +25924,48 @@
     <row r="588">
       <c r="A588" s="2" t="inlineStr">
         <is>
-          <t>BESTE</t>
+          <t>ALTIN</t>
         </is>
       </c>
       <c r="B588" s="3" t="n">
-        <v>30.7</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="C588" s="4" t="n">
-        <v>-0.0007000000000000001</v>
+        <v>-0.009399999999999999</v>
       </c>
       <c r="D588" s="5" t="n">
-        <v>26120000</v>
+        <v>10710000</v>
       </c>
       <c r="E588" s="2" t="inlineStr"/>
       <c r="F588" s="3" t="n">
-        <v>68.69</v>
+        <v>43.25</v>
       </c>
       <c r="G588" s="2" t="inlineStr"/>
       <c r="H588" s="2" t="inlineStr"/>
       <c r="I588" s="2" t="inlineStr"/>
       <c r="J588" s="2" t="inlineStr"/>
-      <c r="K588" s="2" t="inlineStr">
-        <is>
-          <t>Elektrik, Su, Gaz Hizmetleri</t>
-        </is>
-      </c>
-      <c r="L588" s="2" t="inlineStr">
-        <is>
-          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
-        </is>
-      </c>
+      <c r="K588" s="2" t="inlineStr"/>
+      <c r="L588" s="2" t="inlineStr"/>
       <c r="M588" s="2" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" s="6" t="inlineStr">
         <is>
-          <t>ENPRA</t>
+          <t>MARMR</t>
         </is>
       </c>
       <c r="B589" s="7" t="n">
-        <v>79.3</v>
+        <v>2.88</v>
       </c>
       <c r="C589" s="8" t="n">
-        <v>-0.021</v>
+        <v>-0.0368</v>
       </c>
       <c r="D589" s="9" t="n">
-        <v>171630</v>
+        <v>190570000</v>
       </c>
       <c r="E589" s="6" t="inlineStr"/>
       <c r="F589" s="7" t="n">
-        <v>11.3</v>
+        <v>52.36</v>
       </c>
       <c r="G589" s="6" t="inlineStr"/>
       <c r="H589" s="6" t="inlineStr"/>
@@ -25994,38 +25976,36 @@
           <t>Finans</t>
         </is>
       </c>
-      <c r="L589" s="6" t="inlineStr"/>
+      <c r="L589" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
+        </is>
+      </c>
       <c r="M589" s="6" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" s="2" t="inlineStr">
         <is>
-          <t>BORLS</t>
+          <t>LXGYO</t>
         </is>
       </c>
       <c r="B590" s="3" t="n">
-        <v>6.34</v>
+        <v>17.89</v>
       </c>
       <c r="C590" s="4" t="n">
-        <v>-0.0745</v>
+        <v>-0.0438</v>
       </c>
       <c r="D590" s="5" t="n">
-        <v>57090000</v>
-      </c>
-      <c r="E590" s="4" t="n">
-        <v>0.1672</v>
-      </c>
+        <v>66660000</v>
+      </c>
+      <c r="E590" s="2" t="inlineStr"/>
       <c r="F590" s="3" t="n">
-        <v>51.71</v>
+        <v>54.49</v>
       </c>
       <c r="G590" s="2" t="inlineStr"/>
       <c r="H590" s="2" t="inlineStr"/>
-      <c r="I590" s="4" t="n">
-        <v>-5.3262</v>
-      </c>
-      <c r="J590" s="4" t="n">
-        <v>-4.2562</v>
-      </c>
+      <c r="I590" s="2" t="inlineStr"/>
+      <c r="J590" s="2" t="inlineStr"/>
       <c r="K590" s="2" t="inlineStr">
         <is>
           <t>Finans</t>
@@ -26033,7 +26013,7 @@
       </c>
       <c r="L590" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST GAYRİMENKUL YO, BIST HALKA ARZ, BIST MALİ, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M590" s="2" t="inlineStr"/>
@@ -26041,60 +26021,60 @@
     <row r="591">
       <c r="A591" s="6" t="inlineStr">
         <is>
-          <t>UCAYM</t>
+          <t>BRMEN</t>
         </is>
       </c>
       <c r="B591" s="7" t="n">
-        <v>31.36</v>
+        <v>9.6</v>
       </c>
       <c r="C591" s="8" t="n">
-        <v>0.0058</v>
+        <v>-0.0194</v>
       </c>
       <c r="D591" s="9" t="n">
-        <v>14110000</v>
+        <v>961350</v>
       </c>
       <c r="E591" s="8" t="n">
-        <v>0.2667</v>
+        <v>0.95</v>
       </c>
       <c r="F591" s="7" t="n">
-        <v>60.8</v>
+        <v>60.81</v>
       </c>
       <c r="G591" s="6" t="inlineStr"/>
       <c r="H591" s="6" t="inlineStr"/>
-      <c r="I591" s="6" t="inlineStr"/>
-      <c r="J591" s="6" t="inlineStr"/>
+      <c r="I591" s="8" t="n">
+        <v>-23.6291</v>
+      </c>
+      <c r="J591" s="8" t="n">
+        <v>-0.4678</v>
+      </c>
       <c r="K591" s="6" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
-        </is>
-      </c>
-      <c r="L591" s="6" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L591" s="6" t="inlineStr"/>
       <c r="M591" s="6" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" s="2" t="inlineStr">
         <is>
-          <t>ICUGS</t>
+          <t>UCAYM</t>
         </is>
       </c>
       <c r="B592" s="3" t="n">
-        <v>6.06</v>
+        <v>31.36</v>
       </c>
       <c r="C592" s="4" t="n">
-        <v>-0.008199999999999999</v>
+        <v>0.0058</v>
       </c>
       <c r="D592" s="5" t="n">
-        <v>44330000</v>
+        <v>14110000</v>
       </c>
       <c r="E592" s="4" t="n">
-        <v>0.8667</v>
+        <v>0.2667</v>
       </c>
       <c r="F592" s="3" t="n">
-        <v>67.06999999999999</v>
+        <v>60.8</v>
       </c>
       <c r="G592" s="2" t="inlineStr"/>
       <c r="H592" s="2" t="inlineStr"/>
@@ -26102,12 +26082,12 @@
       <c r="J592" s="2" t="inlineStr"/>
       <c r="K592" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="L592" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
+          <t>BIST TUM-100, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M592" s="2" t="inlineStr"/>
@@ -26185,34 +26165,40 @@
     <row r="595">
       <c r="A595" s="6" t="inlineStr">
         <is>
-          <t>CGCAM</t>
+          <t>GRNYO</t>
         </is>
       </c>
       <c r="B595" s="7" t="n">
-        <v>45.46</v>
+        <v>19.78</v>
       </c>
       <c r="C595" s="8" t="n">
-        <v>0.0102</v>
+        <v>-0.0639</v>
       </c>
       <c r="D595" s="9" t="n">
-        <v>6120000</v>
-      </c>
-      <c r="E595" s="6" t="inlineStr"/>
+        <v>711640</v>
+      </c>
+      <c r="E595" s="8" t="n">
+        <v>0.9869</v>
+      </c>
       <c r="F595" s="7" t="n">
-        <v>67.47</v>
+        <v>60.87</v>
       </c>
       <c r="G595" s="6" t="inlineStr"/>
       <c r="H595" s="6" t="inlineStr"/>
-      <c r="I595" s="6" t="inlineStr"/>
-      <c r="J595" s="6" t="inlineStr"/>
+      <c r="I595" s="8" t="n">
+        <v>-0.2446</v>
+      </c>
+      <c r="J595" s="8" t="n">
+        <v>0.3246</v>
+      </c>
       <c r="K595" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı tüketim malları</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L595" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST TAŞ TOPRAK, BIST HALKA ARZ, BIST ANA, BIST MANİSA</t>
+          <t>BIST MENKUL KIYM YO</t>
         </is>
       </c>
       <c r="M595" s="6" t="inlineStr"/>
@@ -26220,137 +26206,163 @@
     <row r="596">
       <c r="A596" s="2" t="inlineStr">
         <is>
-          <t>FRMPL</t>
+          <t>MMCAS</t>
         </is>
       </c>
       <c r="B596" s="3" t="n">
-        <v>35.76</v>
+        <v>76.8</v>
       </c>
       <c r="C596" s="4" t="n">
-        <v>-0.0245</v>
+        <v>-0.0235</v>
       </c>
       <c r="D596" s="5" t="n">
-        <v>5260000</v>
-      </c>
-      <c r="E596" s="2" t="inlineStr"/>
+        <v>60180</v>
+      </c>
+      <c r="E596" s="4" t="n">
+        <v>0.58</v>
+      </c>
       <c r="F596" s="3" t="n">
-        <v>59.16</v>
+        <v>43.15</v>
       </c>
       <c r="G596" s="2" t="inlineStr"/>
       <c r="H596" s="2" t="inlineStr"/>
-      <c r="I596" s="2" t="inlineStr"/>
-      <c r="J596" s="2" t="inlineStr"/>
+      <c r="I596" s="4" t="n">
+        <v>-9.409700000000001</v>
+      </c>
+      <c r="J596" s="4" t="n">
+        <v>-4.155</v>
+      </c>
       <c r="K596" s="2" t="inlineStr">
         <is>
-          <t>Üretici imalatı</t>
-        </is>
-      </c>
-      <c r="L596" s="2" t="inlineStr">
-        <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
-        </is>
-      </c>
+          <t>Taşımacılık</t>
+        </is>
+      </c>
+      <c r="L596" s="2" t="inlineStr"/>
       <c r="M596" s="2" t="inlineStr"/>
     </row>
     <row r="597">
       <c r="A597" s="6" t="inlineStr">
         <is>
-          <t>INTEK</t>
+          <t>TCELL</t>
         </is>
       </c>
       <c r="B597" s="7" t="n">
-        <v>244.25</v>
+        <v>115</v>
       </c>
       <c r="C597" s="8" t="n">
-        <v>-0.0338</v>
+        <v>-0.0566</v>
       </c>
       <c r="D597" s="9" t="n">
-        <v>10010</v>
+        <v>21130000</v>
       </c>
       <c r="E597" s="8" t="n">
-        <v>0.2578</v>
+        <v>0.4894</v>
       </c>
       <c r="F597" s="7" t="n">
-        <v>45.91</v>
-      </c>
-      <c r="G597" s="6" t="inlineStr"/>
+        <v>50.2</v>
+      </c>
+      <c r="G597" s="7" t="n">
+        <v>13.6</v>
+      </c>
       <c r="H597" s="6" t="inlineStr"/>
-      <c r="I597" s="6" t="inlineStr"/>
-      <c r="J597" s="6" t="inlineStr"/>
+      <c r="I597" s="8" t="n">
+        <v>0.0735</v>
+      </c>
+      <c r="J597" s="8" t="n">
+        <v>0.1091</v>
+      </c>
       <c r="K597" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
-        </is>
-      </c>
-      <c r="L597" s="6" t="inlineStr"/>
+          <t>İletişim</t>
+        </is>
+      </c>
+      <c r="L597" s="6" t="inlineStr">
+        <is>
+          <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST İLETİŞİM, BIST HİZMETLER, BIST İSTANBUL, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500, STOXX Eastern Europe 50</t>
+        </is>
+      </c>
       <c r="M597" s="6" t="inlineStr"/>
     </row>
     <row r="598">
       <c r="A598" s="2" t="inlineStr">
         <is>
-          <t>DMLKT</t>
+          <t>LILAK</t>
         </is>
       </c>
       <c r="B598" s="3" t="n">
-        <v>6.12</v>
+        <v>35.16</v>
       </c>
       <c r="C598" s="4" t="n">
-        <v>-0.006500000000000001</v>
+        <v>-0.0228</v>
       </c>
       <c r="D598" s="5" t="n">
-        <v>7340000</v>
-      </c>
-      <c r="E598" s="2" t="inlineStr"/>
+        <v>5700000</v>
+      </c>
+      <c r="E598" s="4" t="n">
+        <v>0.3528</v>
+      </c>
       <c r="F598" s="3" t="n">
-        <v>53.81</v>
-      </c>
-      <c r="G598" s="2" t="inlineStr"/>
+        <v>42.83</v>
+      </c>
+      <c r="G598" s="3" t="n">
+        <v>13.9</v>
+      </c>
       <c r="H598" s="2" t="inlineStr"/>
-      <c r="I598" s="2" t="inlineStr"/>
-      <c r="J598" s="2" t="inlineStr"/>
+      <c r="I598" s="4" t="n">
+        <v>0.1029</v>
+      </c>
+      <c r="J598" s="4" t="n">
+        <v>-1.4864</v>
+      </c>
       <c r="K598" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
-        </is>
-      </c>
-      <c r="L598" s="2" t="inlineStr"/>
+          <t>Dayanıklı olmayan tüketici ürünleri</t>
+        </is>
+      </c>
+      <c r="L598" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST ORMAN KAĞIT BASIM, BIST YILDIZ, BIST TEMETTU, BIST KURUMSAL YÖNETİM, BIST TEKİRDAĞ</t>
+        </is>
+      </c>
       <c r="M598" s="2" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" s="6" t="inlineStr">
         <is>
-          <t>NETAS</t>
+          <t>ARZUM</t>
         </is>
       </c>
       <c r="B599" s="7" t="n">
-        <v>70.15000000000001</v>
+        <v>2.63</v>
       </c>
       <c r="C599" s="8" t="n">
-        <v>-0.0134</v>
+        <v>-0.0295</v>
       </c>
       <c r="D599" s="9" t="n">
-        <v>862740</v>
+        <v>28760000</v>
       </c>
       <c r="E599" s="8" t="n">
-        <v>0.3695000000000001</v>
+        <v>0.7119</v>
       </c>
       <c r="F599" s="7" t="n">
-        <v>64.09</v>
+        <v>41.18</v>
       </c>
       <c r="G599" s="6" t="inlineStr"/>
       <c r="H599" s="6" t="inlineStr"/>
-      <c r="I599" s="6" t="inlineStr"/>
+      <c r="I599" s="8" t="n">
+        <v>-191.6342</v>
+      </c>
       <c r="J599" s="8" t="n">
-        <v>0.1431</v>
+        <v>-0.8093</v>
       </c>
       <c r="K599" s="6" t="inlineStr">
         <is>
-          <t>Teknoloji hizmetleri</t>
+          <t>Dağıtım servisleri</t>
         </is>
       </c>
       <c r="L599" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST İSTANBUL, BIST ANA, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M599" s="6" t="inlineStr"/>
@@ -26358,42 +26370,40 @@
     <row r="600">
       <c r="A600" s="2" t="inlineStr">
         <is>
-          <t>TCELL</t>
+          <t>CRFSA</t>
         </is>
       </c>
       <c r="B600" s="3" t="n">
-        <v>115</v>
+        <v>148.6</v>
       </c>
       <c r="C600" s="4" t="n">
-        <v>-0.0566</v>
+        <v>-0.0237</v>
       </c>
       <c r="D600" s="5" t="n">
-        <v>21130000</v>
+        <v>1120000</v>
       </c>
       <c r="E600" s="4" t="n">
-        <v>0.4894</v>
+        <v>0.1071</v>
       </c>
       <c r="F600" s="3" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="G600" s="3" t="n">
-        <v>13.6</v>
-      </c>
+        <v>51.67</v>
+      </c>
+      <c r="G600" s="2" t="inlineStr"/>
       <c r="H600" s="2" t="inlineStr"/>
       <c r="I600" s="4" t="n">
-        <v>0.0735</v>
+        <v>-3.6635</v>
       </c>
       <c r="J600" s="4" t="n">
-        <v>0.1091</v>
+        <v>-0.4897</v>
       </c>
       <c r="K600" s="2" t="inlineStr">
         <is>
-          <t>İletişim</t>
+          <t>Perakende satış</t>
         </is>
       </c>
       <c r="L600" s="2" t="inlineStr">
         <is>
-          <t>BIST 100, BIST 30, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST 50, BIST İLETİŞİM, BIST HİZMETLER, BIST İSTANBUL, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST TEMETTU 25, BIST TEMETTU, BIST SÜRDÜRÜLEBİLİRLİK, BIST SÜRDÜRÜLEBİLİRLİK 25, BIST 30 AĞIRLIK SINIRLAMALI 10, BIST 30 EŞİT AĞIRLIKLI GETİRİ, BIST 30 AĞIRLIK SINIRLAMALI 25, STOXX Emerging Markets 1500, STOXX Eastern Europe 50</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
         </is>
       </c>
       <c r="M600" s="2" t="inlineStr"/>
@@ -26401,34 +26411,26 @@
     <row r="601">
       <c r="A601" s="6" t="inlineStr">
         <is>
-          <t>BERA</t>
+          <t>FRMPL</t>
         </is>
       </c>
       <c r="B601" s="7" t="n">
-        <v>17.39</v>
+        <v>35.76</v>
       </c>
       <c r="C601" s="8" t="n">
-        <v>-0.023</v>
+        <v>-0.0245</v>
       </c>
       <c r="D601" s="9" t="n">
-        <v>16640000</v>
-      </c>
-      <c r="E601" s="8" t="n">
-        <v>0.9246</v>
-      </c>
+        <v>5260000</v>
+      </c>
+      <c r="E601" s="6" t="inlineStr"/>
       <c r="F601" s="7" t="n">
-        <v>49.27</v>
-      </c>
-      <c r="G601" s="7" t="n">
-        <v>164.37</v>
-      </c>
+        <v>59.16</v>
+      </c>
+      <c r="G601" s="6" t="inlineStr"/>
       <c r="H601" s="6" t="inlineStr"/>
-      <c r="I601" s="8" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="J601" s="8" t="n">
-        <v>-10.3171</v>
-      </c>
+      <c r="I601" s="6" t="inlineStr"/>
+      <c r="J601" s="6" t="inlineStr"/>
       <c r="K601" s="6" t="inlineStr">
         <is>
           <t>Üretici imalatı</t>
@@ -26436,7 +26438,7 @@
       </c>
       <c r="L601" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
+          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST HALKA ARZ, BIST KATILIM TÜM, BIST ANA, BIST TEKİRDAĞ</t>
         </is>
       </c>
       <c r="M601" s="6" t="inlineStr"/>
@@ -26444,21 +26446,21 @@
     <row r="602">
       <c r="A602" s="2" t="inlineStr">
         <is>
-          <t>SMRVA</t>
+          <t>BESTE</t>
         </is>
       </c>
       <c r="B602" s="3" t="n">
-        <v>18.01</v>
+        <v>30.7</v>
       </c>
       <c r="C602" s="4" t="n">
-        <v>-0.0317</v>
+        <v>-0.0007000000000000001</v>
       </c>
       <c r="D602" s="5" t="n">
-        <v>61370000</v>
+        <v>26120000</v>
       </c>
       <c r="E602" s="2" t="inlineStr"/>
       <c r="F602" s="3" t="n">
-        <v>52.71</v>
+        <v>68.69</v>
       </c>
       <c r="G602" s="2" t="inlineStr"/>
       <c r="H602" s="2" t="inlineStr"/>
@@ -26466,12 +26468,12 @@
       <c r="J602" s="2" t="inlineStr"/>
       <c r="K602" s="2" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Elektrik, Su, Gaz Hizmetleri</t>
         </is>
       </c>
       <c r="L602" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
+          <t>BIST ELEKTRIK, BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST HİZMETLER, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA</t>
         </is>
       </c>
       <c r="M602" s="2" t="inlineStr"/>
@@ -26479,34 +26481,38 @@
     <row r="603">
       <c r="A603" s="6" t="inlineStr">
         <is>
-          <t>MCARD</t>
+          <t>NETAS</t>
         </is>
       </c>
       <c r="B603" s="7" t="n">
-        <v>203.2</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="C603" s="8" t="n">
-        <v>0.0114</v>
+        <v>-0.0134</v>
       </c>
       <c r="D603" s="9" t="n">
-        <v>7230000</v>
-      </c>
-      <c r="E603" s="6" t="inlineStr"/>
+        <v>862740</v>
+      </c>
+      <c r="E603" s="8" t="n">
+        <v>0.3695000000000001</v>
+      </c>
       <c r="F603" s="7" t="n">
-        <v>71.43000000000001</v>
+        <v>64.09</v>
       </c>
       <c r="G603" s="6" t="inlineStr"/>
       <c r="H603" s="6" t="inlineStr"/>
       <c r="I603" s="6" t="inlineStr"/>
-      <c r="J603" s="6" t="inlineStr"/>
+      <c r="J603" s="8" t="n">
+        <v>0.1431</v>
+      </c>
       <c r="K603" s="6" t="inlineStr">
         <is>
-          <t>Ticari hizmetler</t>
+          <t>Teknoloji hizmetleri</t>
         </is>
       </c>
       <c r="L603" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KURUMSAL YÖNETİM</t>
         </is>
       </c>
       <c r="M603" s="6" t="inlineStr"/>
@@ -26514,21 +26520,23 @@
     <row r="604">
       <c r="A604" s="2" t="inlineStr">
         <is>
-          <t>GLRMK</t>
+          <t>INTEK</t>
         </is>
       </c>
       <c r="B604" s="3" t="n">
-        <v>205</v>
+        <v>244.25</v>
       </c>
       <c r="C604" s="4" t="n">
-        <v>0.0029</v>
+        <v>-0.0338</v>
       </c>
       <c r="D604" s="5" t="n">
-        <v>11560000</v>
-      </c>
-      <c r="E604" s="2" t="inlineStr"/>
+        <v>10010</v>
+      </c>
+      <c r="E604" s="4" t="n">
+        <v>0.2578</v>
+      </c>
       <c r="F604" s="3" t="n">
-        <v>53.72</v>
+        <v>45.91</v>
       </c>
       <c r="G604" s="2" t="inlineStr"/>
       <c r="H604" s="2" t="inlineStr"/>
@@ -26536,55 +26544,45 @@
       <c r="J604" s="2" t="inlineStr"/>
       <c r="K604" s="2" t="inlineStr">
         <is>
-          <t>Endüstriyel hizmetler</t>
-        </is>
-      </c>
-      <c r="L604" s="2" t="inlineStr">
-        <is>
-          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
-        </is>
-      </c>
+          <t>İşlenebilen endüstriler</t>
+        </is>
+      </c>
+      <c r="L604" s="2" t="inlineStr"/>
       <c r="M604" s="2" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" s="6" t="inlineStr">
         <is>
-          <t>LILAK</t>
+          <t>ICUGS</t>
         </is>
       </c>
       <c r="B605" s="7" t="n">
-        <v>35.16</v>
+        <v>6.06</v>
       </c>
       <c r="C605" s="8" t="n">
-        <v>-0.0228</v>
+        <v>-0.008199999999999999</v>
       </c>
       <c r="D605" s="9" t="n">
-        <v>5700000</v>
+        <v>44330000</v>
       </c>
       <c r="E605" s="8" t="n">
-        <v>0.3528</v>
+        <v>0.8667</v>
       </c>
       <c r="F605" s="7" t="n">
-        <v>42.83</v>
-      </c>
-      <c r="G605" s="7" t="n">
-        <v>13.9</v>
-      </c>
+        <v>67.06999999999999</v>
+      </c>
+      <c r="G605" s="6" t="inlineStr"/>
       <c r="H605" s="6" t="inlineStr"/>
-      <c r="I605" s="8" t="n">
-        <v>0.1029</v>
-      </c>
-      <c r="J605" s="8" t="n">
-        <v>-1.4864</v>
-      </c>
+      <c r="I605" s="6" t="inlineStr"/>
+      <c r="J605" s="6" t="inlineStr"/>
       <c r="K605" s="6" t="inlineStr">
         <is>
-          <t>Dayanıklı olmayan tüketici ürünleri</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L605" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST HALKA ARZ, BIST ORMAN KAĞIT BASIM, BIST YILDIZ, BIST TEMETTU, BIST KURUMSAL YÖNETİM, BIST TEKİRDAĞ</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST ANA</t>
         </is>
       </c>
       <c r="M605" s="6" t="inlineStr"/>
@@ -26592,40 +26590,34 @@
     <row r="606">
       <c r="A606" s="2" t="inlineStr">
         <is>
-          <t>CRFSA</t>
+          <t>GLRMK</t>
         </is>
       </c>
       <c r="B606" s="3" t="n">
-        <v>148.6</v>
+        <v>205</v>
       </c>
       <c r="C606" s="4" t="n">
-        <v>-0.0237</v>
+        <v>0.0029</v>
       </c>
       <c r="D606" s="5" t="n">
-        <v>1120000</v>
-      </c>
-      <c r="E606" s="4" t="n">
-        <v>0.1071</v>
-      </c>
+        <v>11560000</v>
+      </c>
+      <c r="E606" s="2" t="inlineStr"/>
       <c r="F606" s="3" t="n">
-        <v>51.67</v>
+        <v>53.72</v>
       </c>
       <c r="G606" s="2" t="inlineStr"/>
       <c r="H606" s="2" t="inlineStr"/>
-      <c r="I606" s="4" t="n">
-        <v>-3.6635</v>
-      </c>
-      <c r="J606" s="4" t="n">
-        <v>-0.4897</v>
-      </c>
+      <c r="I606" s="2" t="inlineStr"/>
+      <c r="J606" s="2" t="inlineStr"/>
       <c r="K606" s="2" t="inlineStr">
         <is>
-          <t>Perakende satış</t>
+          <t>Endüstriyel hizmetler</t>
         </is>
       </c>
       <c r="L606" s="2" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST TÜM, BIST TİCARET, BIST HİZMETLER, BIST ANA</t>
+          <t>BIST 100, BIST 100 AĞIRLIK SINIRLAMALI 10, BIST TÜM, BIST İNŞAAT, BIST HALKA ARZ, BIST HİZMETLER, BIST 100-30, BIST KATILIM 100, BIST KATILIM TÜM, BIST 100 AĞIRLIK SINIRLAMALI 25, BIST YILDIZ, BIST KATILIM 50, BIST KATILIM 30, BIST ANKARA, BIST KATILIM 30 EŞİT AĞIRLIKLI GETİRİ</t>
         </is>
       </c>
       <c r="M606" s="2" t="inlineStr"/>
@@ -26633,67 +26625,75 @@
     <row r="607">
       <c r="A607" s="6" t="inlineStr">
         <is>
-          <t>ALTIN</t>
+          <t>BORLS</t>
         </is>
       </c>
       <c r="B607" s="7" t="n">
-        <v>80.04000000000001</v>
+        <v>6.34</v>
       </c>
       <c r="C607" s="8" t="n">
-        <v>-0.009399999999999999</v>
+        <v>-0.0745</v>
       </c>
       <c r="D607" s="9" t="n">
-        <v>10710000</v>
-      </c>
-      <c r="E607" s="6" t="inlineStr"/>
+        <v>57090000</v>
+      </c>
+      <c r="E607" s="8" t="n">
+        <v>0.1672</v>
+      </c>
       <c r="F607" s="7" t="n">
-        <v>43.25</v>
+        <v>51.71</v>
       </c>
       <c r="G607" s="6" t="inlineStr"/>
       <c r="H607" s="6" t="inlineStr"/>
-      <c r="I607" s="6" t="inlineStr"/>
-      <c r="J607" s="6" t="inlineStr"/>
-      <c r="K607" s="6" t="inlineStr"/>
-      <c r="L607" s="6" t="inlineStr"/>
+      <c r="I607" s="8" t="n">
+        <v>-5.3262</v>
+      </c>
+      <c r="J607" s="8" t="n">
+        <v>-4.2562</v>
+      </c>
+      <c r="K607" s="6" t="inlineStr">
+        <is>
+          <t>Finans</t>
+        </is>
+      </c>
+      <c r="L607" s="6" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST HİZMETLER, BIST İSTANBUL, BIST YILDIZ</t>
+        </is>
+      </c>
       <c r="M607" s="6" t="inlineStr"/>
     </row>
     <row r="608">
       <c r="A608" s="2" t="inlineStr">
         <is>
-          <t>GRNYO</t>
+          <t>MCARD</t>
         </is>
       </c>
       <c r="B608" s="3" t="n">
-        <v>19.78</v>
+        <v>203.2</v>
       </c>
       <c r="C608" s="4" t="n">
-        <v>-0.0639</v>
+        <v>0.0114</v>
       </c>
       <c r="D608" s="5" t="n">
-        <v>711640</v>
-      </c>
-      <c r="E608" s="4" t="n">
-        <v>0.9869</v>
-      </c>
+        <v>7230000</v>
+      </c>
+      <c r="E608" s="2" t="inlineStr"/>
       <c r="F608" s="3" t="n">
-        <v>60.87</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="G608" s="2" t="inlineStr"/>
       <c r="H608" s="2" t="inlineStr"/>
-      <c r="I608" s="4" t="n">
-        <v>-0.2446</v>
-      </c>
-      <c r="J608" s="4" t="n">
-        <v>0.3246</v>
-      </c>
+      <c r="I608" s="2" t="inlineStr"/>
+      <c r="J608" s="2" t="inlineStr"/>
       <c r="K608" s="2" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Ticari hizmetler</t>
         </is>
       </c>
       <c r="L608" s="2" t="inlineStr">
         <is>
-          <t>BIST MENKUL KIYM YO</t>
+          <t>BIST TUM-100, BIST TÜM, BIST TEKNOLOJİ, BIST BILISIM, BIST HALKA ARZ, BIST İSTANBUL, BIST KATILIM TÜM, BIST ANA, BIST TEMETTU, BIST TEKNOLOJI AĞIRLIK SINIRLAMALI, BIST KATILIM TEMETTU</t>
         </is>
       </c>
       <c r="M608" s="2" t="inlineStr"/>
@@ -26701,34 +26701,42 @@
     <row r="609">
       <c r="A609" s="6" t="inlineStr">
         <is>
-          <t>MARMR</t>
+          <t>BERA</t>
         </is>
       </c>
       <c r="B609" s="7" t="n">
-        <v>2.88</v>
+        <v>17.39</v>
       </c>
       <c r="C609" s="8" t="n">
-        <v>-0.0368</v>
+        <v>-0.023</v>
       </c>
       <c r="D609" s="9" t="n">
-        <v>190570000</v>
-      </c>
-      <c r="E609" s="6" t="inlineStr"/>
+        <v>16640000</v>
+      </c>
+      <c r="E609" s="8" t="n">
+        <v>0.9246</v>
+      </c>
       <c r="F609" s="7" t="n">
-        <v>52.36</v>
-      </c>
-      <c r="G609" s="6" t="inlineStr"/>
+        <v>49.27</v>
+      </c>
+      <c r="G609" s="7" t="n">
+        <v>164.37</v>
+      </c>
       <c r="H609" s="6" t="inlineStr"/>
-      <c r="I609" s="6" t="inlineStr"/>
-      <c r="J609" s="6" t="inlineStr"/>
+      <c r="I609" s="8" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="J609" s="8" t="n">
+        <v>-10.3171</v>
+      </c>
       <c r="K609" s="6" t="inlineStr">
         <is>
-          <t>Finans</t>
+          <t>Üretici imalatı</t>
         </is>
       </c>
       <c r="L609" s="6" t="inlineStr">
         <is>
-          <t>BIST TUM-100, BIST SINAI, BIST TÜM, BIST KİMYA PETROL PLASTİK, BIST ANA, BIST KOCAELI</t>
+          <t>BIST TUM-100, BIST TÜM, BIST HOLDING VE YATIRIM, BIST MALİ, BIST KATILIM 100, BIST KATILIM TÜM, BIST YILDIZ, BIST KATILIM 50, BIST KONYA</t>
         </is>
       </c>
       <c r="M609" s="6" t="inlineStr"/>
@@ -26736,72 +26744,64 @@
     <row r="610">
       <c r="A610" s="2" t="inlineStr">
         <is>
-          <t>MMCAS</t>
+          <t>SMRVA</t>
         </is>
       </c>
       <c r="B610" s="3" t="n">
-        <v>76.8</v>
+        <v>18.01</v>
       </c>
       <c r="C610" s="4" t="n">
-        <v>-0.0235</v>
+        <v>-0.0317</v>
       </c>
       <c r="D610" s="5" t="n">
-        <v>60180</v>
-      </c>
-      <c r="E610" s="4" t="n">
-        <v>0.58</v>
-      </c>
+        <v>61370000</v>
+      </c>
+      <c r="E610" s="2" t="inlineStr"/>
       <c r="F610" s="3" t="n">
-        <v>43.15</v>
+        <v>52.71</v>
       </c>
       <c r="G610" s="2" t="inlineStr"/>
       <c r="H610" s="2" t="inlineStr"/>
-      <c r="I610" s="4" t="n">
-        <v>-9.409700000000001</v>
-      </c>
-      <c r="J610" s="4" t="n">
-        <v>-4.155</v>
-      </c>
+      <c r="I610" s="2" t="inlineStr"/>
+      <c r="J610" s="2" t="inlineStr"/>
       <c r="K610" s="2" t="inlineStr">
         <is>
-          <t>Taşımacılık</t>
-        </is>
-      </c>
-      <c r="L610" s="2" t="inlineStr"/>
+          <t>Ticari hizmetler</t>
+        </is>
+      </c>
+      <c r="L610" s="2" t="inlineStr">
+        <is>
+          <t>BIST TUM-100, BIST TÜM, BIST HALKA ARZ, BIST MALİ, BIST ANA, BIST TEMETTU</t>
+        </is>
+      </c>
       <c r="M610" s="2" t="inlineStr"/>
     </row>
     <row r="611">
       <c r="A611" s="6" t="inlineStr">
         <is>
-          <t>BRMEN</t>
+          <t>DMLKT</t>
         </is>
       </c>
       <c r="B611" s="7" t="n">
-        <v>9.6</v>
+        <v>6.12</v>
       </c>
       <c r="C611" s="8" t="n">
-        <v>-0.0194</v>
+        <v>-0.006500000000000001</v>
       </c>
       <c r="D611" s="9" t="n">
-        <v>961350</v>
-      </c>
-      <c r="E611" s="8" t="n">
-        <v>0.95</v>
-      </c>
+        <v>7340000</v>
+      </c>
+      <c r="E611" s="6" t="inlineStr"/>
       <c r="F611" s="7" t="n">
-        <v>60.81</v>
+        <v>53.81</v>
       </c>
       <c r="G611" s="6" t="inlineStr"/>
       <c r="H611" s="6" t="inlineStr"/>
-      <c r="I611" s="8" t="n">
-        <v>-23.6291</v>
-      </c>
-      <c r="J611" s="8" t="n">
-        <v>-0.4678</v>
-      </c>
+      <c r="I611" s="6" t="inlineStr"/>
+      <c r="J611" s="6" t="inlineStr"/>
       <c r="K611" s="6" t="inlineStr">
         <is>
-          <t>İşlenebilen endüstriler</t>
+          <t>Finans</t>
         </is>
       </c>
       <c r="L611" s="6" t="inlineStr"/>
@@ -26829,7 +26829,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>12.05.2026 16:30</t>
+          <t>12.05.2026 17:31</t>
         </is>
       </c>
     </row>
